--- a/dosokai-life/data/events.xlsx
+++ b/dosokai-life/data/events.xlsx
@@ -4475,7 +4475,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー;フラグ:管理職;手応え&gt;=70</t>
+          <t>キャリア=商社|メーカー|IT企業|銀行・保険|電力・鉄道;フラグ:管理職;手応え&gt;=70</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="F79" s="6" t="n"/>
       <c r="G79" s="6" t="n">
-        <v>6e-05</v>
+        <v>0.00012</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="G80" s="6" t="n">
-        <v>6.499999999999999e-05</v>
+        <v>0.00015</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W122"/>
+  <dimension ref="A1:W152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -11920,7 +11920,7 @@
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>画面で商社／メーカー／市役所から2つ選ぶ。浪人・休学したら22歳</t>
+          <t>画面で「届いた求人」（大卒6件・高卒5件、実際の就職先の割合でくじ引き）から2つ選ぶ。浪人・休学したら22歳</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>パートナー=交際中;交際年数&gt;=1</t>
+          <t>パートナー=交際中;交際年数&gt;=1;!経過:結婚を保留&lt;2</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -12287,9 +12287,11 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>二人で同じ店に通うようになって、もうすぐ〔交際年数&gt;=3〕三年〔それ以外〕一年〔/〕になる。
+          <t>〔!フラグ:結婚を保留;交際年数&gt;=3〕二人で同じ店に通うようになって、もうすぐ三年になる。〔/〕〔!フラグ:結婚を保留;交際年数&lt;3〕二人で同じ店に通うようになって、もうすぐ一年になる。〔/〕〔!フラグ:結婚を保留〕
 店主が、何も言わずに二人分のお茶を出すようになった。
-「そろそろ、ちゃんと考えない？」と言われたのは、帰りの信号待ちだった。</t>
+「そろそろ、ちゃんと考えない？」と言われたのは、帰りの信号待ちだった。〔/〕〔フラグ:結婚を保留〕前に「まだ決められない」と答えてから、二年がたった。
+パートナーは、そのことを一度も責めなかった。
+誕生日の夜、ケーキのろうそくを吹き消したあとで、「もう一度だけ聞くね」と前置きされた。〔/〕</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -12304,12 +12306,12 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>まだ決められない</t>
+          <t>〔!フラグ:結婚を保留〕まだ決められない〔それ以外〕もう少しだけ待ってほしい〔/〕</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>余白-2</t>
+          <t>フラグ:結婚を保留 余白-2</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -12325,13 +12327,17 @@
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>v0.2：交際している相手がいるときだけ起きる。出会いは E100</t>
+          <t>交際している相手がいるときだけ起きる。「まだ決められない」を選ぶと、2年あけて別の場面でもう一度聞かれる（同じ場面が続かないように）</t>
         </is>
       </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
-      <c r="U17" s="6" t="n"/>
+      <c r="U17" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:結婚を保留→×1.5</t>
+        </is>
+      </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
           <t>立ち絵:パートナー/照れ/右</t>
@@ -14629,7 +14635,11 @@
       <c r="R52" s="6" t="n"/>
       <c r="S52" s="6" t="n"/>
       <c r="T52" s="6" t="n"/>
-      <c r="U52" s="6" t="n"/>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:結婚を保留→×1.3</t>
+        </is>
+      </c>
       <c r="V52" s="6" t="n"/>
       <c r="W52" s="6" t="n"/>
     </row>
@@ -16967,7 +16977,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>親の介護=あり;キャリア=商社|メーカー|市役所|地元企業|非正規|自営業|再雇用</t>
+          <t>親の介護=あり;働き方=会社員|公務員|非正規|自営業|再雇用</t>
         </is>
       </c>
       <c r="F87" s="6" t="n">
@@ -17434,7 +17444,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業|非正規|自営業</t>
+          <t>働き方=会社員|公務員|非正規|自営業</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
@@ -17517,7 +17527,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業;手応え&gt;=55;!フラグ:管理職</t>
+          <t>働き方=会社員|公務員;手応え&gt;=55;!フラグ:管理職</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -17638,7 +17648,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業;!フラグ:管理職</t>
+          <t>働き方=会社員|公務員;!フラグ:管理職</t>
         </is>
       </c>
       <c r="F97" s="6" t="n">
@@ -17718,7 +17728,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|地元企業</t>
+          <t>働き方=会社員;!キャリア=農業・漁業</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -17808,7 +17818,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業</t>
+          <t>働き方=会社員|公務員</t>
         </is>
       </c>
       <c r="F99" s="6" t="n">
@@ -18899,7 +18909,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業|非正規|自営業;!キャリア=自営業</t>
+          <t>働き方=会社員|公務員|非正規</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
@@ -18993,7 +19003,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業|非正規|自営業</t>
+          <t>働き方=会社員|公務員|非正規|自営業</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -19159,7 +19169,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>キャリア=商社|メーカー|市役所|地元企業|非正規|自営業;!地域=海外</t>
+          <t>働き方=会社員|公務員|非正規|自営業;!地域=海外</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
@@ -19457,12 +19467,12 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>E900</t>
+          <t>E600</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>運命</t>
+          <t>一行</t>
         </is>
       </c>
       <c r="C122" s="6" t="n">
@@ -19471,23 +19481,23 @@
       <c r="D122" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>表:死亡</t>
-        </is>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=IT企業</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>0.3</v>
       </c>
       <c r="G122" s="6" t="n"/>
       <c r="H122" s="6" t="inlineStr">
         <is>
-          <t>終わり</t>
+          <t>IT企業</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>〔フラグ:持病がん〕病室の窓から、いつもの町の屋根が見えた。〔/〕〔フラグ:循環器;!フラグ:持病がん〕その朝は、いつもと同じ朝のはずだった。〔/〕〔!フラグ:持病がん;!フラグ:循環器〕それは、思いがけない形でやってきた。〔/〕
-〔パートナー=既婚〕最後に手を握っていたのは、パートナーだった。〔/〕〔子ども数&gt;=1;!パートナー=既婚〕子どもが、ずっとそばにいてくれた。〔/〕
-あなたの人生は、{年齢}歳で終わった。</t>
+          <t>障害対応の電話は、いつも金曜の夜十時に鳴る。</t>
         </is>
       </c>
       <c r="J122" s="6" t="n"/>
@@ -19498,24 +19508,1950 @@
       <c r="O122" s="6" t="n"/>
       <c r="P122" s="6" t="inlineStr">
         <is>
-          <t>処理:本人の死</t>
-        </is>
-      </c>
-      <c r="Q122" s="6" t="inlineStr">
-        <is>
-          <t>生命表で引く。65歳までに約8％（男10.4％・女5.6％）。健康や病気の倍率の平均が1になるよう、はじめに全体へ×0.72をかけている。静かに短く描く</t>
-        </is>
-      </c>
+          <t>健康-1 手応え+1</t>
+        </is>
+      </c>
+      <c r="Q122" s="6" t="n"/>
       <c r="R122" s="6" t="n"/>
       <c r="S122" s="6" t="n"/>
       <c r="T122" s="6" t="n"/>
-      <c r="U122" s="6" t="inlineStr">
-        <is>
-          <t>年齢&gt;=0→×0.72／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×3／フラグ:循環器→×2／体質=弱い→×1.2</t>
-        </is>
-      </c>
+      <c r="U122" s="6" t="n"/>
       <c r="V122" s="6" t="n"/>
       <c r="W122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>E601</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=IT企業</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>リリース前夜</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>新しいサービスの公開は、明日の朝九時。
+オフィスの窓の外が、もう明るくなりかけていた。
+画面の隅の小さなエラーが、まだ一つだけ消えない。</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>徹夜で直す</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>健康-5 手応え+6</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>チームに任せて、帰って寝る</t>
+        </is>
+      </c>
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>余白+2 つながり+2</t>
+        </is>
+      </c>
+      <c r="N123" s="6" t="inlineStr">
+        <is>
+          <t>公開を一日延ばすよう掛け合う</t>
+        </is>
+      </c>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>手応え+2 余白-2</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="n"/>
+      <c r="Q123" s="6" t="n"/>
+      <c r="R123" s="6" t="n"/>
+      <c r="S123" s="6" t="n"/>
+      <c r="T123" s="6" t="n"/>
+      <c r="U123" s="6" t="n"/>
+      <c r="V123" s="6" t="n"/>
+      <c r="W123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>E602</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D124" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=銀行・保険</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G124" s="6" t="n"/>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>銀行・保険</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>月末の窓口は、印鑑と通帳の音で埋まる。</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="n"/>
+      <c r="K124" s="6" t="n"/>
+      <c r="L124" s="6" t="n"/>
+      <c r="M124" s="6" t="n"/>
+      <c r="N124" s="6" t="n"/>
+      <c r="O124" s="6" t="n"/>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>手応え+1</t>
+        </is>
+      </c>
+      <c r="Q124" s="6" t="n"/>
+      <c r="R124" s="6" t="n"/>
+      <c r="S124" s="6" t="n"/>
+      <c r="T124" s="6" t="n"/>
+      <c r="U124" s="6" t="n"/>
+      <c r="V124" s="6" t="n"/>
+      <c r="W124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>E603</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D125" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=銀行・保険</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>ノルマ</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>支店の壁に、営業成績のグラフが貼り出された。
+自分の棒は、下から三番目だった。</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>知り合いに頭を下げて回る</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>お金+3 つながり-4 余白-3</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>自分のやり方を変えない</t>
+        </is>
+      </c>
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>手応え-2 余白+1</t>
+        </is>
+      </c>
+      <c r="N125" s="6" t="inlineStr">
+        <is>
+          <t>異動を願い出る</t>
+        </is>
+      </c>
+      <c r="O125" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:異動希望 余白-1</t>
+        </is>
+      </c>
+      <c r="P125" s="6" t="n"/>
+      <c r="Q125" s="6" t="n"/>
+      <c r="R125" s="6" t="n"/>
+      <c r="S125" s="6" t="n"/>
+      <c r="T125" s="6" t="n"/>
+      <c r="U125" s="6" t="n"/>
+      <c r="V125" s="6" t="n"/>
+      <c r="W125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>E604</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D126" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=小売・販売</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G126" s="6" t="n"/>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>小売・販売</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>閉店後の売り場で、明日のチラシの値札を三百枚つけ替えた。</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="n"/>
+      <c r="K126" s="6" t="n"/>
+      <c r="L126" s="6" t="n"/>
+      <c r="M126" s="6" t="n"/>
+      <c r="N126" s="6" t="n"/>
+      <c r="O126" s="6" t="n"/>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>健康-1 つながり+1</t>
+        </is>
+      </c>
+      <c r="Q126" s="6" t="n"/>
+      <c r="R126" s="6" t="n"/>
+      <c r="S126" s="6" t="n"/>
+      <c r="T126" s="6" t="n"/>
+      <c r="U126" s="6" t="n"/>
+      <c r="V126" s="6" t="n"/>
+      <c r="W126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>E605</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D127" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=小売・販売</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>店長代理</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>店長が倒れて、来週から店を任されることになった。
+レジの鍵束が、思っていたより重かった。</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="n"/>
+      <c r="K127" s="6" t="n"/>
+      <c r="L127" s="6" t="n"/>
+      <c r="M127" s="6" t="n"/>
+      <c r="N127" s="6" t="n"/>
+      <c r="O127" s="6" t="n"/>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>手応え+6 余白-5 お金+2</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="n"/>
+      <c r="R127" s="6" t="n"/>
+      <c r="S127" s="6" t="n"/>
+      <c r="T127" s="6" t="n"/>
+      <c r="U127" s="6" t="n"/>
+      <c r="V127" s="6" t="n"/>
+      <c r="W127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>E606</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=病院・介護</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G128" s="6" t="n"/>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>病院・介護</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>夜勤明けの朝、自販機のコーヒーがいちばんうまい。</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="n"/>
+      <c r="K128" s="6" t="n"/>
+      <c r="L128" s="6" t="n"/>
+      <c r="M128" s="6" t="n"/>
+      <c r="N128" s="6" t="n"/>
+      <c r="O128" s="6" t="n"/>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>健康-1 手応え+1</t>
+        </is>
+      </c>
+      <c r="Q128" s="6" t="n"/>
+      <c r="R128" s="6" t="n"/>
+      <c r="S128" s="6" t="n"/>
+      <c r="T128" s="6" t="n"/>
+      <c r="U128" s="6" t="n"/>
+      <c r="V128" s="6" t="n"/>
+      <c r="W128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>E607</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D129" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=病院・介護</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>見送り</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>担当していたおばあさんが、夜明け前に静かに息を引き取った。
+前の日、「ありがとうね」と三回言われたのを、まだ覚えている。</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n"/>
+      <c r="K129" s="6" t="n"/>
+      <c r="L129" s="6" t="n"/>
+      <c r="M129" s="6" t="n"/>
+      <c r="N129" s="6" t="n"/>
+      <c r="O129" s="6" t="n"/>
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>手応え+4 余白-4 つながり+2</t>
+        </is>
+      </c>
+      <c r="Q129" s="6" t="n"/>
+      <c r="R129" s="6" t="n"/>
+      <c r="S129" s="6" t="n"/>
+      <c r="T129" s="6" t="n"/>
+      <c r="U129" s="6" t="n"/>
+      <c r="V129" s="6" t="n"/>
+      <c r="W129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>E608</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D130" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=学校の先生</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>学校の先生</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>テストの丸つけの赤ペンが、一晩で一本なくなった。</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="n"/>
+      <c r="K130" s="6" t="n"/>
+      <c r="L130" s="6" t="n"/>
+      <c r="M130" s="6" t="n"/>
+      <c r="N130" s="6" t="n"/>
+      <c r="O130" s="6" t="n"/>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>手応え+1 余白-1</t>
+        </is>
+      </c>
+      <c r="Q130" s="6" t="n"/>
+      <c r="R130" s="6" t="n"/>
+      <c r="S130" s="6" t="n"/>
+      <c r="T130" s="6" t="n"/>
+      <c r="U130" s="6" t="n"/>
+      <c r="V130" s="6" t="n"/>
+      <c r="W130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>E609</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D131" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=学校の先生</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>卒業式</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>初めて担任をしたクラスの卒業式。
+名前を呼ぶ声が、三十二人目で少しだけ震えた。</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="n"/>
+      <c r="K131" s="6" t="n"/>
+      <c r="L131" s="6" t="n"/>
+      <c r="M131" s="6" t="n"/>
+      <c r="N131" s="6" t="n"/>
+      <c r="O131" s="6" t="n"/>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>手応え+6 つながり+4 余白+2</t>
+        </is>
+      </c>
+      <c r="Q131" s="6" t="n"/>
+      <c r="R131" s="6" t="n"/>
+      <c r="S131" s="6" t="n"/>
+      <c r="T131" s="6" t="n"/>
+      <c r="U131" s="6" t="n"/>
+      <c r="V131" s="6" t="n"/>
+      <c r="W131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>E610</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D132" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=建設会社</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G132" s="6" t="n"/>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>建設会社</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>現場の朝礼は七時半。ラジオ体操の音が、まだ暗い空に響いた。</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="n"/>
+      <c r="K132" s="6" t="n"/>
+      <c r="L132" s="6" t="n"/>
+      <c r="M132" s="6" t="n"/>
+      <c r="N132" s="6" t="n"/>
+      <c r="O132" s="6" t="n"/>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>健康+1 手応え+1</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="n"/>
+      <c r="R132" s="6" t="n"/>
+      <c r="S132" s="6" t="n"/>
+      <c r="T132" s="6" t="n"/>
+      <c r="U132" s="6" t="n"/>
+      <c r="V132" s="6" t="n"/>
+      <c r="W132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>E611</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D133" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=建設会社</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>竣工</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>二年かかった建物の、足場が外れた。
+下から見上げると、自分の知らない建物みたいだった。</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="n"/>
+      <c r="K133" s="6" t="n"/>
+      <c r="L133" s="6" t="n"/>
+      <c r="M133" s="6" t="n"/>
+      <c r="N133" s="6" t="n"/>
+      <c r="O133" s="6" t="n"/>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>手応え+8 お金+3</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="n"/>
+      <c r="R133" s="6" t="n"/>
+      <c r="S133" s="6" t="n"/>
+      <c r="T133" s="6" t="n"/>
+      <c r="U133" s="6" t="n"/>
+      <c r="V133" s="6" t="n"/>
+      <c r="W133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>E612</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D134" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=研究・専門職</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G134" s="6" t="n"/>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>研究・専門職</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>図面の線を一本直すのに、三日かかった。</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n"/>
+      <c r="K134" s="6" t="n"/>
+      <c r="L134" s="6" t="n"/>
+      <c r="M134" s="6" t="n"/>
+      <c r="N134" s="6" t="n"/>
+      <c r="O134" s="6" t="n"/>
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>手応え+1 余白-1</t>
+        </is>
+      </c>
+      <c r="Q134" s="6" t="n"/>
+      <c r="R134" s="6" t="n"/>
+      <c r="S134" s="6" t="n"/>
+      <c r="T134" s="6" t="n"/>
+      <c r="U134" s="6" t="n"/>
+      <c r="V134" s="6" t="n"/>
+      <c r="W134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>E613</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D135" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=研究・専門職</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>大きな案件</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>事務所に、これまででいちばん大きな依頼が来た。
+所長は「おまえがやれ」とだけ言った。</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>引き受ける</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>手応え+8 余白-6 お金+3</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>先輩と組ませてもらう</t>
+        </is>
+      </c>
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>手応え+4 つながり+3</t>
+        </is>
+      </c>
+      <c r="N135" s="6" t="inlineStr">
+        <is>
+          <t>今の仕事で手一杯だと伝える</t>
+        </is>
+      </c>
+      <c r="O135" s="6" t="inlineStr">
+        <is>
+          <t>余白+2 手応え-2</t>
+        </is>
+      </c>
+      <c r="P135" s="6" t="n"/>
+      <c r="Q135" s="6" t="n"/>
+      <c r="R135" s="6" t="n"/>
+      <c r="S135" s="6" t="n"/>
+      <c r="T135" s="6" t="n"/>
+      <c r="U135" s="6" t="n"/>
+      <c r="V135" s="6" t="n"/>
+      <c r="W135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>E614</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D136" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=運送・物流</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G136" s="6" t="n"/>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>運送・物流</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>深夜の高速のサービスエリアで、知らない運転手とうどんをすすった。</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="n"/>
+      <c r="K136" s="6" t="n"/>
+      <c r="L136" s="6" t="n"/>
+      <c r="M136" s="6" t="n"/>
+      <c r="N136" s="6" t="n"/>
+      <c r="O136" s="6" t="n"/>
+      <c r="P136" s="6" t="inlineStr">
+        <is>
+          <t>つながり+1 健康-1</t>
+        </is>
+      </c>
+      <c r="Q136" s="6" t="n"/>
+      <c r="R136" s="6" t="n"/>
+      <c r="S136" s="6" t="n"/>
+      <c r="T136" s="6" t="n"/>
+      <c r="U136" s="6" t="n"/>
+      <c r="V136" s="6" t="n"/>
+      <c r="W136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>E615</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D137" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=運送・物流</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>時間の上限</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>運転できる時間に、上限が決められた。
+体は楽になった。給与明細の数字は、少し減った。</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="n"/>
+      <c r="K137" s="6" t="n"/>
+      <c r="L137" s="6" t="n"/>
+      <c r="M137" s="6" t="n"/>
+      <c r="N137" s="6" t="n"/>
+      <c r="O137" s="6" t="n"/>
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>健康+4 余白+3 お金-3</t>
+        </is>
+      </c>
+      <c r="Q137" s="6" t="n"/>
+      <c r="R137" s="6" t="n"/>
+      <c r="S137" s="6" t="n"/>
+      <c r="T137" s="6" t="n"/>
+      <c r="U137" s="6" t="n"/>
+      <c r="V137" s="6" t="n"/>
+      <c r="W137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>E616</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D138" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=ホテル・飲食</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G138" s="6" t="n"/>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>ホテル・飲食</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>年末の宴会場で、四百人分の乾杯のグラスを並べた。</t>
+        </is>
+      </c>
+      <c r="J138" s="6" t="n"/>
+      <c r="K138" s="6" t="n"/>
+      <c r="L138" s="6" t="n"/>
+      <c r="M138" s="6" t="n"/>
+      <c r="N138" s="6" t="n"/>
+      <c r="O138" s="6" t="n"/>
+      <c r="P138" s="6" t="inlineStr">
+        <is>
+          <t>健康-1 つながり+1</t>
+        </is>
+      </c>
+      <c r="Q138" s="6" t="n"/>
+      <c r="R138" s="6" t="n"/>
+      <c r="S138" s="6" t="n"/>
+      <c r="T138" s="6" t="n"/>
+      <c r="U138" s="6" t="n"/>
+      <c r="V138" s="6" t="n"/>
+      <c r="W138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>E617</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D139" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=ホテル・飲食</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>手紙</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>フロントに、宿泊客から手紙が届いた。
+「あの夜の対応を、家族で今でも話しています」
+名前の欄に、自分の名前が書いてあった。</t>
+        </is>
+      </c>
+      <c r="J139" s="6" t="n"/>
+      <c r="K139" s="6" t="n"/>
+      <c r="L139" s="6" t="n"/>
+      <c r="M139" s="6" t="n"/>
+      <c r="N139" s="6" t="n"/>
+      <c r="O139" s="6" t="n"/>
+      <c r="P139" s="6" t="inlineStr">
+        <is>
+          <t>手応え+5 余白+4</t>
+        </is>
+      </c>
+      <c r="Q139" s="6" t="n"/>
+      <c r="R139" s="6" t="n"/>
+      <c r="S139" s="6" t="n"/>
+      <c r="T139" s="6" t="n"/>
+      <c r="U139" s="6" t="n"/>
+      <c r="V139" s="6" t="n"/>
+      <c r="W139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>E618</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=美容・サービス</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G140" s="6" t="n"/>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>美容・サービス</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>鏡越しに、お客さんが「いつもの」と言った。</t>
+        </is>
+      </c>
+      <c r="J140" s="6" t="n"/>
+      <c r="K140" s="6" t="n"/>
+      <c r="L140" s="6" t="n"/>
+      <c r="M140" s="6" t="n"/>
+      <c r="N140" s="6" t="n"/>
+      <c r="O140" s="6" t="n"/>
+      <c r="P140" s="6" t="inlineStr">
+        <is>
+          <t>つながり+1 手応え+1</t>
+        </is>
+      </c>
+      <c r="Q140" s="6" t="n"/>
+      <c r="R140" s="6" t="n"/>
+      <c r="S140" s="6" t="n"/>
+      <c r="T140" s="6" t="n"/>
+      <c r="U140" s="6" t="n"/>
+      <c r="V140" s="6" t="n"/>
+      <c r="W140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>E619</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D141" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=美容・サービス</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>独立の誘い</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>常連のお客さんが言った。
+「あなたが自分の店を出したら、そっちに行くよ」
+本気かどうかは、わからなかった。</t>
+        </is>
+      </c>
+      <c r="J141" s="6" t="inlineStr">
+        <is>
+          <t>店を出す</t>
+        </is>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>キャリア:自営業 フラグ:開業 フラグ:転機 お金-12 手応え+8</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>今の店で続ける</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>余白+1</t>
+        </is>
+      </c>
+      <c r="N141" s="6" t="inlineStr">
+        <is>
+          <t>いつかのために貯金を始める</t>
+        </is>
+      </c>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 余白-1</t>
+        </is>
+      </c>
+      <c r="P141" s="6" t="n"/>
+      <c r="Q141" s="6" t="n"/>
+      <c r="R141" s="6" t="inlineStr">
+        <is>
+          <t>お金&gt;=35</t>
+        </is>
+      </c>
+      <c r="S141" s="6" t="n"/>
+      <c r="T141" s="6" t="n"/>
+      <c r="U141" s="6" t="n"/>
+      <c r="V141" s="6" t="n"/>
+      <c r="W141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>E620</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=不動産</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G142" s="6" t="n"/>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>内見の帰り、空き家のポストに、前の住人宛ての年賀状が一枚残っていた。</t>
+        </is>
+      </c>
+      <c r="J142" s="6" t="n"/>
+      <c r="K142" s="6" t="n"/>
+      <c r="L142" s="6" t="n"/>
+      <c r="M142" s="6" t="n"/>
+      <c r="N142" s="6" t="n"/>
+      <c r="O142" s="6" t="n"/>
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>余白-1</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="n"/>
+      <c r="R142" s="6" t="n"/>
+      <c r="S142" s="6" t="n"/>
+      <c r="T142" s="6" t="n"/>
+      <c r="U142" s="6" t="n"/>
+      <c r="V142" s="6" t="n"/>
+      <c r="W142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>E621</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=不動産</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>大きな契約</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>一億円を超える物件の契約書に、はんこが押された。
+帰りの電車で、手のひらにまだ朱肉の色が残っていた。</t>
+        </is>
+      </c>
+      <c r="J143" s="6" t="n"/>
+      <c r="K143" s="6" t="n"/>
+      <c r="L143" s="6" t="n"/>
+      <c r="M143" s="6" t="n"/>
+      <c r="N143" s="6" t="n"/>
+      <c r="O143" s="6" t="n"/>
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>お金+8 手応え+5 余白-2</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="n"/>
+      <c r="R143" s="6" t="n"/>
+      <c r="S143" s="6" t="n"/>
+      <c r="T143" s="6" t="n"/>
+      <c r="U143" s="6" t="n"/>
+      <c r="V143" s="6" t="n"/>
+      <c r="W143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>E622</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=電力・鉄道</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>電力・鉄道</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>台風の夜、制服のまま朝まで待機した。</t>
+        </is>
+      </c>
+      <c r="J144" s="6" t="n"/>
+      <c r="K144" s="6" t="n"/>
+      <c r="L144" s="6" t="n"/>
+      <c r="M144" s="6" t="n"/>
+      <c r="N144" s="6" t="n"/>
+      <c r="O144" s="6" t="n"/>
+      <c r="P144" s="6" t="inlineStr">
+        <is>
+          <t>健康-1 つながり+1</t>
+        </is>
+      </c>
+      <c r="Q144" s="6" t="n"/>
+      <c r="R144" s="6" t="n"/>
+      <c r="S144" s="6" t="n"/>
+      <c r="T144" s="6" t="n"/>
+      <c r="U144" s="6" t="n"/>
+      <c r="V144" s="6" t="n"/>
+      <c r="W144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>E623</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=電力・鉄道</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>転勤</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>県の端の営業所への転勤が決まった。
+「三年で戻れるから」と言われた。前の人は、五年いたらしい。</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>家族で引っ越す</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>つながり-2 余白-2</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>一人で行く</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>つながり-4 お金+2</t>
+        </is>
+      </c>
+      <c r="N145" s="6" t="inlineStr">
+        <is>
+          <t>転勤のない部署を希望する</t>
+        </is>
+      </c>
+      <c r="O145" s="6" t="inlineStr">
+        <is>
+          <t>手応え-3 余白+2</t>
+        </is>
+      </c>
+      <c r="P145" s="6" t="n"/>
+      <c r="Q145" s="6" t="n"/>
+      <c r="R145" s="6" t="inlineStr">
+        <is>
+          <t>パートナー=既婚</t>
+        </is>
+      </c>
+      <c r="S145" s="6" t="n"/>
+      <c r="T145" s="6" t="n"/>
+      <c r="U145" s="6" t="n"/>
+      <c r="V145" s="6" t="n"/>
+      <c r="W145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>E624</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=農業・漁業</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G146" s="6" t="n"/>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>農業・漁業</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>日の出より先に起きる暮らしに、体がすっかり慣れた。</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="n"/>
+      <c r="K146" s="6" t="n"/>
+      <c r="L146" s="6" t="n"/>
+      <c r="M146" s="6" t="n"/>
+      <c r="N146" s="6" t="n"/>
+      <c r="O146" s="6" t="n"/>
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>健康+1 手応え+1</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="n"/>
+      <c r="R146" s="6" t="n"/>
+      <c r="S146" s="6" t="n"/>
+      <c r="T146" s="6" t="n"/>
+      <c r="U146" s="6" t="n"/>
+      <c r="V146" s="6" t="n"/>
+      <c r="W146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>E625</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D147" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=農業・漁業</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>天気</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>その年は、天気に恵まれなかった。
+秋の帳簿の数字は、去年の半分だった。</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>来年に備えて、作り方を変える</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>手応え+4 お金-4</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>副業で補う</t>
+        </is>
+      </c>
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 余白-4</t>
+        </is>
+      </c>
+      <c r="N147" s="6" t="inlineStr">
+        <is>
+          <t>組合の仲間と助け合う</t>
+        </is>
+      </c>
+      <c r="O147" s="6" t="inlineStr">
+        <is>
+          <t>つながり+5 お金-2</t>
+        </is>
+      </c>
+      <c r="P147" s="6" t="n"/>
+      <c r="Q147" s="6" t="n"/>
+      <c r="R147" s="6" t="n"/>
+      <c r="S147" s="6" t="n"/>
+      <c r="T147" s="6" t="n"/>
+      <c r="U147" s="6" t="n"/>
+      <c r="V147" s="6" t="n"/>
+      <c r="W147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>E660</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D148" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>会社の運命=成長;働き方=会社員</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>追い風</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>会社の業績が、三年続けて過去最高を更新した。
+社長の年頭のあいさつが、いつもより五分長かった。</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="n"/>
+      <c r="K148" s="6" t="n"/>
+      <c r="L148" s="6" t="n"/>
+      <c r="M148" s="6" t="n"/>
+      <c r="N148" s="6" t="n"/>
+      <c r="O148" s="6" t="n"/>
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>お金+6 手応え+4</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="n"/>
+      <c r="R148" s="6" t="n"/>
+      <c r="S148" s="6" t="n"/>
+      <c r="T148" s="6" t="n"/>
+      <c r="U148" s="6" t="n"/>
+      <c r="V148" s="6" t="n"/>
+      <c r="W148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>E661</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D149" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>会社の運命=再編;働き方=会社員</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>再編</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>会社が、同業の大手と一つになることが決まった。
+説明会の最後に、新しい社名のロゴが映し出された。</t>
+        </is>
+      </c>
+      <c r="J149" s="6" t="inlineStr">
+        <is>
+          <t>新しい組織で続ける</t>
+        </is>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>余白-4 手応え+2</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>この機会に転職活動をする</t>
+        </is>
+      </c>
+      <c r="M149" s="6" t="inlineStr">
+        <is>
+          <t>処理:転職判定</t>
+        </is>
+      </c>
+      <c r="N149" s="6" t="inlineStr">
+        <is>
+          <t>早期退職の上乗せに手を挙げる</t>
+        </is>
+      </c>
+      <c r="O149" s="6" t="inlineStr">
+        <is>
+          <t>キャリア:無職 お金+10 余白+3</t>
+        </is>
+      </c>
+      <c r="P149" s="6" t="n"/>
+      <c r="Q149" s="6" t="n"/>
+      <c r="R149" s="6" t="n"/>
+      <c r="S149" s="6" t="n"/>
+      <c r="T149" s="6" t="n"/>
+      <c r="U149" s="6" t="n"/>
+      <c r="V149" s="6" t="n"/>
+      <c r="W149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>E662</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>会社の運命=業績不振;働き方=会社員</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>冬のボーナス</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>冬のボーナスは、出なかった。
+給与明細の「賞与」の欄に、ゼロが一つだけ印刷されていた。</t>
+        </is>
+      </c>
+      <c r="J150" s="6" t="inlineStr">
+        <is>
+          <t>耐えて続ける</t>
+        </is>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>お金-4 余白-3</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>転職活動を始める</t>
+        </is>
+      </c>
+      <c r="M150" s="6" t="inlineStr">
+        <is>
+          <t>処理:転職判定</t>
+        </is>
+      </c>
+      <c r="N150" s="6" t="inlineStr">
+        <is>
+          <t>副業を始める</t>
+        </is>
+      </c>
+      <c r="O150" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 余白-5 手応え+2</t>
+        </is>
+      </c>
+      <c r="P150" s="6" t="n"/>
+      <c r="Q150" s="6" t="n"/>
+      <c r="R150" s="6" t="n"/>
+      <c r="S150" s="6" t="n"/>
+      <c r="T150" s="6" t="n"/>
+      <c r="U150" s="6" t="n"/>
+      <c r="V150" s="6" t="n"/>
+      <c r="W150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>E663</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D151" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>会社の運命=人手不足</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>人が足りない</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>同僚が二人続けて辞め、穴は埋まらないままだった。
+休みの日にも、職場の電話が鳴るようになった。</t>
+        </is>
+      </c>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>引き受けて回す</t>
+        </is>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>手応え+3 健康-5 余白-5</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>上に掛け合って人を増やしてもらう</t>
+        </is>
+      </c>
+      <c r="M151" s="6" t="inlineStr">
+        <is>
+          <t>つながり+2 余白-2</t>
+        </is>
+      </c>
+      <c r="N151" s="6" t="inlineStr">
+        <is>
+          <t>自分も辞めることを考える</t>
+        </is>
+      </c>
+      <c r="O151" s="6" t="inlineStr">
+        <is>
+          <t>処理:転職判定</t>
+        </is>
+      </c>
+      <c r="P151" s="6" t="n"/>
+      <c r="Q151" s="6" t="n"/>
+      <c r="R151" s="6" t="n"/>
+      <c r="S151" s="6" t="n"/>
+      <c r="T151" s="6" t="n"/>
+      <c r="U151" s="6" t="n"/>
+      <c r="V151" s="6" t="n"/>
+      <c r="W151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>E900</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E152" s="6" t="n"/>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>表:死亡</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="n"/>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>終わり</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>〔フラグ:持病がん〕病室の窓から、いつもの町の屋根が見えた。〔/〕〔フラグ:循環器;!フラグ:持病がん〕その朝は、いつもと同じ朝のはずだった。〔/〕〔!フラグ:持病がん;!フラグ:循環器〕それは、思いがけない形でやってきた。〔/〕
+〔パートナー=既婚〕最後に手を握っていたのは、パートナーだった。〔/〕〔子ども数&gt;=1;!パートナー=既婚〕子どもが、ずっとそばにいてくれた。〔/〕
+あなたの人生は、{年齢}歳で終わった。</t>
+        </is>
+      </c>
+      <c r="J152" s="6" t="n"/>
+      <c r="K152" s="6" t="n"/>
+      <c r="L152" s="6" t="n"/>
+      <c r="M152" s="6" t="n"/>
+      <c r="N152" s="6" t="n"/>
+      <c r="O152" s="6" t="n"/>
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>処理:本人の死</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
+        <is>
+          <t>生命表で引く。65歳までに約8％（男10.4％・女5.6％）。健康や病気の倍率の平均が1になるよう、はじめに全体へ×0.72をかけている。静かに短く描く</t>
+        </is>
+      </c>
+      <c r="R152" s="6" t="n"/>
+      <c r="S152" s="6" t="n"/>
+      <c r="T152" s="6" t="n"/>
+      <c r="U152" s="6" t="inlineStr">
+        <is>
+          <t>年齢&gt;=0→×0.72／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×3／フラグ:循環器→×2／体質=弱い→×1.2</t>
+        </is>
+      </c>
+      <c r="V152" s="6" t="n"/>
+      <c r="W152" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23263,7 +25199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23305,6 +25241,56 @@
           <t>会社の運命（仮の確率）</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>業種</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>大卒の割合</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>高卒の割合</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>大卒のみ</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>合格率</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>景気の影響</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>出典</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>会社の例</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>求人の見出し</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -23337,6 +25323,20 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>学生</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="6" t="n"/>
+      <c r="L2" s="6" t="n"/>
+      <c r="M2" s="6" t="n"/>
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="6" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -23346,7 +25346,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>大学卒のみ。基本合格率0.15</t>
+          <t>大学卒のみ</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -23369,6 +25369,44 @@
           <t>安泰50% ／ 資源バブル20% ／ 撤退20% ／ 不祥事10%</t>
         </is>
       </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>卸売（商社）</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>総合商社,食品の専門商社,鉄鋼の専門商社</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -23378,7 +25416,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>大学卒・高卒とも。基本合格率0.45</t>
+          <t>大学卒・高卒とも</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -23393,7 +25431,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>大きな落ち込みは少ないが、会社の運命に左右される</t>
+          <t>会社の運命に左右される</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -23401,6 +25439,42 @@
           <t>安泰40% ／ 合併25% ／ 工場閉鎖20% ／ ヒット15%</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>製造業</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>自動車部品,食品工場,電子部品,化学メーカー,精密機械,住宅設備,印刷,製薬</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -23410,7 +25484,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>大学卒・高卒とも。基本合格率0.35（不況ほど狭き門）</t>
+          <t>大学卒・高卒とも（公務員試験）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -23431,6 +25505,46 @@
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>平穏60% ／ 大災害20% ／ 財政難20%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>公務員</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>公務</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>市役所,県庁,町役場,警察・消防</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>公務員</t>
         </is>
       </c>
     </row>
@@ -23465,6 +25579,24 @@
           <t>安泰40% ／ 後継者不在30% ／ 事業拡大30%</t>
         </is>
       </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>地元の中小企業</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -23497,6 +25629,20 @@
           <t>なし（毎年、雇い止めの判定 E080）</t>
         </is>
       </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>非正規</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -23529,6 +25675,20 @@
           <t>軌道に乗る40% ／ 細く長く35% ／ 閉店25%</t>
         </is>
       </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自営業</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -23561,6 +25721,20 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>無職</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -23593,6 +25767,20 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>再雇用</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -23625,6 +25813,912 @@
           <t>—</t>
         </is>
       </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>引退</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>IT企業</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>大学卒が中心</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 手応え+2 健康-1 余白-1</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>手応え・お金</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>健康・余白</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>安泰35% ／ 成長30% ／ 再編20% ／ 業績不振15%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>情報通信</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>ソフトウェア開発,通信会社,ウェブサービス,システム会社</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>銀行・保険</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>大学卒が中心</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>お金+3 手応え+1 余白-1</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>お金</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>余白</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>安泰45% ／ 再編35% ／ 業績不振20%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>金融・保険</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>地方銀行,信用金庫,生命保険,損害保険,証券会社</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>小売・販売</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>お金+1 つながり+1 余白-1</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>つながり</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>余白・お金</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>安泰40% ／ 成長15% ／ 再編20% ／ 業績不振25%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>小売</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>スーパー,ドラッグストア,家電量販店,ホームセンター,百貨店,コンビニ本部,車のディーラー</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>病院・介護</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも（資格をとる）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>手応え+2 つながり+1 健康-1 余白-1</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>手応え・つながり</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>健康・余白</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>平穏50% ／ 人手不足50%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>医療・福祉</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>小さい</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>総合病院,介護施設,保育園,クリニック,福祉施設</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>学校の先生</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>大学卒のみ（教員採用試験）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>手応え+2 つながり+1 余白-2</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>手応え・つながり</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>余白</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>平穏55% ／ 人手不足45%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>公務員</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>教育</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>小さい</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>小学校,中学校,高校</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>教員</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>建設会社</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 手応え+1 健康-1</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>お金・手応え</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>安泰40% ／ 成長25% ／ 業績不振35%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>建設</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>総合建設,電気工事,設備工事,住宅メーカー</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>研究・専門職</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>大学卒のみ（設計事務所・会計事務所・研究所など）</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>お金+1 手応え+3 余白-1</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>手応え</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>余白</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>安泰45% ／ 成長30% ／ 業績不振25%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>学術研究・専門・技術サービス</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>設計事務所,会計事務所,研究所,広告制作</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>運送・物流</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>お金+1 つながり+1 健康-1</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>お金</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>安泰40% ／ 人手不足40% ／ 業績不振20%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>運輸・郵便</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>運送会社,物流センター,郵便,バス会社</t>
+        </is>
+      </c>
+      <c r="P19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>ホテル・飲食</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>つながり+2 健康-1 余白-1</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>つながり</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>健康・余白</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>安泰30% ／ 成長20% ／ 業績不振30% ／ 人手不足20%</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>宿泊・飲食サービス</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>ホテル,旅館,レストラン,居酒屋チェーン</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>美容・サービス</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>つながり+2 手応え+1 余白-1</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>つながり・手応え</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>余白</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>安泰40% ／ 成長20% ／ 業績不振40%</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>生活関連サービス・そのほかのサービス</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>ふつう</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>美容室,ブライダル,警備会社,人材サービス,スポーツクラブ</t>
+        </is>
+      </c>
+      <c r="P21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>大学卒が中心</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>お金+3 手応え+1 余白-2</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>お金</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>余白</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>安泰40% ／ 成長25% ／ 業績不振35%</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>大きい</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>不動産仲介,ハウスメーカーの営業,マンション管理</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>電力・鉄道</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも（狭き門）</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>お金+2 余白+1</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>お金・余白</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>手応え</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>安泰80% ／ 再編20%</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>電気・ガス・鉄道</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>小さい</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>電力会社,ガス会社,鉄道会社</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>農業・漁業</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>大学卒・高卒とも</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>手応え+2 健康+1 つながり+1 お金-1</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>健康・つながり</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>お金</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>安泰50% ／ 業績不振50%</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>会社員</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>農業・漁業（法人）</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>小さい</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>大卒：2019年春卒 学校基本調査（卸売・小売15.3％、医療・福祉12.7％、製造業12.1％、情報通信10.4％、教育7.3％、金融・保険6.8％、公務6.1％）。ほかは推計／高卒：2016年3月卒 厚生労働省の集計（製造業 約42％、卸売・小売 約14％、建設 約8％）。ほかは推計。合格率・景気の影響はゲームの設計。求人の届きやすさは「割合 ÷ 合格率」</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>農業法人,漁業協同組合,牧場</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25849,7 +28943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26539,6 +29633,188 @@
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t>推計：新卒3年以内離職率（大卒33.8％・高卒37.9％）と転職者比率から</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>大卒の最初の仕事：製造業（メーカー）</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=メーカー@25|進路=大学</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>2019年春卒 学校基本調査</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>大卒の最初の仕事：卸売・小売（商社・小売・販売）</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=商社|小売・販売@25|進路=大学</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>大卒の最初の仕事：医療・福祉</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=病院・介護@25|進路=大学</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>大卒の最初の仕事：情報通信</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=IT企業@25|進路=大学</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>高卒の最初の仕事：製造業（メーカー）</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=メーカー@25|進路=就職</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>2016年3月卒 厚生労働省の集計</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>高卒の最初の仕事：卸売・小売</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=小売・販売@25|進路=就職</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>高卒の最初の仕事：建設</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>最初の仕事=建設会社@25|進路=就職</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
         </is>
       </c>
     </row>

--- a/dosokai-life/data/events.xlsx
+++ b/dosokai-life/data/events.xlsx
@@ -11193,7 +11193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM203"/>
+  <dimension ref="A1:AM206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>フラグ:持病がん;経過:持病がん&gt;=5</t>
+          <t>フラグ:持病がん;!フラグ:がん再発;経過:持病がん&gt;=5</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
@@ -24803,7 +24803,7 @@
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>E900</t>
+          <t>E260</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
@@ -24817,51 +24817,265 @@
       <c r="D203" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="E203" s="6" t="n"/>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:持病がん;!フラグ:がん再発</t>
+        </is>
+      </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>表:死亡</t>
+          <t>表:がんの再発</t>
         </is>
       </c>
       <c r="G203" s="6" t="n"/>
       <c r="H203" s="6" t="inlineStr">
         <is>
-          <t>終わり</t>
+          <t>再発</t>
         </is>
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t>〔フラグ:持病がん〕病室の窓から、いつもの町の屋根が見えた。〔/〕〔フラグ:循環器;!フラグ:持病がん〕その朝は、いつもと同じ朝のはずだった。〔/〕〔!フラグ:持病がん;!フラグ:循環器〕それは、思いがけない形でやってきた。〔/〕
-〔パートナー=既婚〕最後に手を握っていたのは、パートナーだった。〔/〕〔子ども数&gt;=1;!パートナー=既婚〕子どもが、ずっとそばにいてくれた。〔/〕
-あなたの人生は、{年齢}歳で終わった。</t>
-        </is>
-      </c>
-      <c r="J203" s="6" t="n"/>
-      <c r="K203" s="6" t="n"/>
-      <c r="L203" s="6" t="n"/>
-      <c r="M203" s="6" t="n"/>
-      <c r="N203" s="6" t="n"/>
-      <c r="O203" s="6" t="n"/>
-      <c r="P203" s="6" t="inlineStr">
-        <is>
-          <t>処理:本人の死</t>
-        </is>
-      </c>
-      <c r="Q203" s="6" t="inlineStr">
-        <is>
-          <t>生命表で引く。65歳までに約8％（男10.4％・女5.6％）。健康や病気の倍率の平均が1になるよう、はじめに全体へ×0.72をかけている。静かに短く描く</t>
-        </is>
-      </c>
+          <t>定期検査のあと、医師は画像をしばらく黙って見ていた。
+「また、治療をしましょう」
+前のときより、言葉が少なかった。</t>
+        </is>
+      </c>
+      <c r="J203" s="6" t="inlineStr">
+        <is>
+          <t>もう一度、治療に向き合う</t>
+        </is>
+      </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:がん再発 健康-10 お金-6 手応え-4</t>
+        </is>
+      </c>
+      <c r="L203" s="6" t="inlineStr">
+        <is>
+          <t>仕事を減らして、家族との時間を増やす</t>
+        </is>
+      </c>
+      <c r="M203" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:がん再発 健康-8 つながり+6 お金-8</t>
+        </is>
+      </c>
+      <c r="N203" s="6" t="inlineStr">
+        <is>
+          <t>できるだけ、いつもどおりに暮らす</t>
+        </is>
+      </c>
+      <c r="O203" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:がん再発 健康-12 余白+4</t>
+        </is>
+      </c>
+      <c r="P203" s="6" t="n"/>
+      <c r="Q203" s="6" t="n"/>
       <c r="R203" s="6" t="n"/>
       <c r="S203" s="6" t="n"/>
       <c r="T203" s="6" t="n"/>
       <c r="U203" s="6" t="inlineStr">
         <is>
-          <t>年齢&gt;=0→×0.72／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×3／フラグ:循環器→×2／体質=弱い→×1.2</t>
+          <t>健康&lt;30→×1.3</t>
         </is>
       </c>
       <c r="V203" s="6" t="n"/>
-      <c r="W203" s="6" t="n"/>
+      <c r="W203" s="6" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>E261</t>
+        </is>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:がん再発</t>
+        </is>
+      </c>
+      <c r="F204" s="6" t="inlineStr">
+        <is>
+          <t>表:がんの死亡</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="n"/>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>静かな日々</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>治療は、少しずつ痛みをやわらげるためのものに変わっていった。
+窓の外の季節を、ひとつずつ数えるように過ごした。
+あなたの人生は、{年齢}歳で終わった。</t>
+        </is>
+      </c>
+      <c r="J204" s="6" t="n"/>
+      <c r="K204" s="6" t="n"/>
+      <c r="L204" s="6" t="n"/>
+      <c r="M204" s="6" t="n"/>
+      <c r="N204" s="6" t="n"/>
+      <c r="O204" s="6" t="n"/>
+      <c r="P204" s="6" t="inlineStr">
+        <is>
+          <t>処理:本人の死</t>
+        </is>
+      </c>
+      <c r="Q204" s="6" t="n"/>
+      <c r="R204" s="6" t="n"/>
+      <c r="S204" s="6" t="n"/>
+      <c r="T204" s="6" t="n"/>
+      <c r="U204" s="6" t="n"/>
+      <c r="V204" s="6" t="n"/>
+      <c r="W204" s="6" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>E262</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:がん再発;経過:がん再発&gt;=3</t>
+        </is>
+      </c>
+      <c r="F205" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>落ち着いた</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>「数値は落ち着いています」。再発してから三度目の春、医師はそう言った。</t>
+        </is>
+      </c>
+      <c r="J205" s="6" t="n"/>
+      <c r="K205" s="6" t="n"/>
+      <c r="L205" s="6" t="n"/>
+      <c r="M205" s="6" t="n"/>
+      <c r="N205" s="6" t="n"/>
+      <c r="O205" s="6" t="n"/>
+      <c r="P205" s="6" t="inlineStr">
+        <is>
+          <t>フラグ消:がん再発 健康+5 余白+3</t>
+        </is>
+      </c>
+      <c r="Q205" s="6" t="n"/>
+      <c r="R205" s="6" t="n"/>
+      <c r="S205" s="6" t="n"/>
+      <c r="T205" s="6" t="n"/>
+      <c r="U205" s="6" t="n"/>
+      <c r="V205" s="6" t="n"/>
+      <c r="W205" s="6" t="inlineStr">
+        <is>
+          <t>健康</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>E900</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D206" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="6" t="inlineStr">
+        <is>
+          <t>表:死亡</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="n"/>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>終わり</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>〔フラグ:持病がん〕病室の窓から、いつもの町の屋根が見えた。〔/〕〔フラグ:循環器;!フラグ:持病がん〕その朝は、いつもと同じ朝のはずだった。〔/〕〔!フラグ:持病がん;!フラグ:循環器〕それは、思いがけない形でやってきた。〔/〕
+〔パートナー=既婚〕最後に手を握っていたのは、パートナーだった。〔/〕〔子ども数&gt;=1;!パートナー=既婚〕子どもが、ずっとそばにいてくれた。〔/〕
+あなたの人生は、{年齢}歳で終わった。</t>
+        </is>
+      </c>
+      <c r="J206" s="6" t="n"/>
+      <c r="K206" s="6" t="n"/>
+      <c r="L206" s="6" t="n"/>
+      <c r="M206" s="6" t="n"/>
+      <c r="N206" s="6" t="n"/>
+      <c r="O206" s="6" t="n"/>
+      <c r="P206" s="6" t="inlineStr">
+        <is>
+          <t>処理:本人の死</t>
+        </is>
+      </c>
+      <c r="Q206" s="6" t="inlineStr">
+        <is>
+          <t>生命表で引く。65歳までに約8％（男10.4％・女5.6％）。健康や病気の倍率の平均が1になるよう、はじめに全体へ×0.72をかけている。静かに短く描く
+×0.46：生命表にはがんの死も入っている。がんの死は E261 が受け持つので、その分を引いた</t>
+        </is>
+      </c>
+      <c r="R206" s="6" t="n"/>
+      <c r="S206" s="6" t="n"/>
+      <c r="T206" s="6" t="n"/>
+      <c r="U206" s="6" t="inlineStr">
+        <is>
+          <t>年齢&gt;=0→×0.46／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×1.5／フラグ:循環器→×2／体質=弱い→×1.2</t>
+        </is>
+      </c>
+      <c r="V206" s="6" t="n"/>
+      <c r="W206" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31432,7 +31646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32689,7 +32903,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="6" t="n">
-        <v>0.0004</v>
+        <v>0.00032</v>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
@@ -32715,7 +32929,7 @@
         <v>39</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0.001</v>
+        <v>0.0008</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
@@ -32741,7 +32955,7 @@
         <v>49</v>
       </c>
       <c r="E50" s="6" t="n">
-        <v>0.0025</v>
+        <v>0.002</v>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
@@ -32767,7 +32981,7 @@
         <v>59</v>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
@@ -32793,7 +33007,7 @@
         <v>65</v>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0.01</v>
+        <v>0.008</v>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
@@ -33630,6 +33844,214 @@
       <c r="F84" s="6" t="inlineStr">
         <is>
           <t>ゲームの調整（推計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>がんの再発</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>国立がん研究センター：5年生存率は全部位で約6割台（2009〜2011年診断で66.4％）、若い人ほど高い。65歳未満で診断された人は約7割が5年後も生存として、診断後の年数ごとの年率に割り振った推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>がんの再発</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>国立がん研究センター：5年生存率は全部位で約6割台（2009〜2011年診断で66.4％）、若い人ほど高い。65歳未満で診断された人は約7割が5年後も生存として、診断後の年数ごとの年率に割り振った推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>がんの再発</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>国立がん研究センター：5年生存率は全部位で約6割台（2009〜2011年診断で66.4％）、若い人ほど高い。65歳未満で診断された人は約7割が5年後も生存として、診断後の年数ごとの年率に割り振った推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>がんの再発</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>国立がん研究センター：5年生存率は全部位で約6割台（2009〜2011年診断で66.4％）、若い人ほど高い。65歳未満で診断された人は約7割が5年後も生存として、診断後の年数ごとの年率に割り振った推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>がんの再発</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>9</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>国立がん研究センター：5年生存率は全部位で約6割台（2009〜2011年診断で66.4％）、若い人ほど高い。65歳未満で診断された人は約7割が5年後も生存として、診断後の年数ごとの年率に割り振った推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>がんの死亡</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>再発・進行したあとの年率（推計）。診断から5年で約3割が亡くなるように合わせた</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>がんの死亡</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>再発・進行したあとの年率（推計）。診断から5年で約3割が亡くなるように合わせた</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>がんの死亡</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>がんの診断からの年数</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>60</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>再発・進行したあとの年率（推計）。診断から5年で約3割が亡くなるように合わせた</t>
         </is>
       </c>
     </row>

--- a/dosokai-life/data/events.xlsx
+++ b/dosokai-life/data/events.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -840,6 +840,48 @@
       <c r="A57" t="inlineStr">
         <is>
           <t>列「選ばれやすさ」：現実でそれぞれの選択肢を選ぶ人の割合（例：45,22,7）。照合（tests/calibrate.js）のときだけ使い、遊ぶ人の選択には影響しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>■ v0.3 で足したこと（性別・同級生）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>主人公の性別：タイトル画面で「男」「女」「運命にまかせる」を選ぶ（?sex=女 でも指定できる）。条件に「性別=女」「性別=男」と書ける</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>確率表の基準に「産む人の年齢」（女性なら本人、男性ならパートナーの年齢）と「がんの診断からの年数」を使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>キャリアシートの列「女性の割合」：その仕事に就く新人のうち女性の割合。男女で求人の届きやすさが変わる（空なら男女同じ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>配偶者シートの年齢差は、条件「性別=男／女」で男女別の割合にしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>同級生シート：一人8通りの人生（A〜H）。同窓会シートの「健太=D」のような行で、それぞれの様子を書く</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM206"/>
+  <dimension ref="A1:AM210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12619,7 +12661,7 @@
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>フラグ:結婚を保留→×1.5</t>
+          <t>フラグ:結婚を保留→×1.5／性別=女→×1.2／性別=男→×0.85</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
@@ -12644,7 +12686,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -12653,7 +12695,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>表:出産</t>
+          <t>表:出産@産む人の年齢</t>
         </is>
       </c>
       <c r="G19" s="4" t="n"/>
@@ -12664,9 +12706,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>〔フラグ:双子直後〕分娩室の外で待っていると、看護師が指を二本立てて出てきた。
+          <t>〔フラグ:双子直後;性別=女〕長い夜が明けて、胸の上に、小さな重さが順番に二つのせられた。
 「お二人とも、元気ですよ」
-二人分の泣き声が、廊下の端まで聞こえていた。〔/〕〔!フラグ:双子直後;子ども数=1〕生まれてきた子の手は、思っていたより熱かった。
+自分の泣き声と、二人分の泣き声が混ざっていた。〔/〕〔フラグ:双子直後;性別=男〕分娩室の外で待っていると、看護師が指を二本立てて出てきた。
+「お二人とも、元気ですよ」
+二人分の泣き声が、廊下の端まで聞こえていた。〔/〕〔!フラグ:双子直後;子ども数=1;性別=女〕長い夜が明けて、胸の上に、熱いかたまりがのせられた。
+握り返される力の強さに、泣きながら笑ってしまった。〔/〕〔!フラグ:双子直後;子ども数=1;性別=男〕生まれてきた子の手は、思っていたより熱かった。
 握り返される力の強さに、意味もなく笑ってしまった。〔/〕〔!フラグ:双子直後;子ども数&gt;=2〕上の子が、新しく来た家族の小さな足を、こわごわと指でつついた。
 「ちっちゃい」と言って、自分の手と見比べていた。〔/〕</t>
         </is>
@@ -14787,7 +14832,7 @@
       <c r="T51" s="6" t="n"/>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>出会い運=高→×1.5／出会い運=低→×0.5／つながり&lt;35→×0.7／フラグ:離婚経験→×0.6／フラグ:死別→×0.4</t>
+          <t>出会い運=高→×1.5／出会い運=低→×0.5／つながり&lt;35→×0.7／フラグ:離婚経験→×0.6／フラグ:死別→×0.4／性別=女→×1.2／性別=男→×0.85</t>
         </is>
       </c>
       <c r="V51" s="6" t="n"/>
@@ -18606,7 +18651,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>キャリア=無職;経過:無職&gt;=1</t>
+          <t>キャリア=無職;経過:無職&gt;=1;!フラグ:子育て専念</t>
         </is>
       </c>
       <c r="F108" s="6" t="n">
@@ -25071,11 +25116,343 @@
       <c r="T206" s="6" t="n"/>
       <c r="U206" s="6" t="inlineStr">
         <is>
-          <t>年齢&gt;=0→×0.46／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×1.5／フラグ:循環器→×2／体質=弱い→×1.2</t>
+          <t>年齢&gt;=0→×0.46／健康&lt;20→×1.8／健康&gt;=50→×0.75／フラグ:持病がん→×1.5／フラグ:循環器→×2／体質=弱い→×1.2／性別=男→×1.45／性別=女→×0.72</t>
         </is>
       </c>
       <c r="V206" s="6" t="n"/>
       <c r="W206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>E136</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>性別=女;フラグ:出産直後;働き方=会社員|公務員|非正規</t>
+        </is>
+      </c>
+      <c r="F207" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>このあと</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>産休に入る前の日、机の引き出しを片づけた。
+上司は「戻ってくるよね」と言った。
+戻るかどうかは、まだ自分でも決めていなかった。</t>
+        </is>
+      </c>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>育休のあと、職場に戻る</t>
+        </is>
+      </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:出産時に就業 フラグ:育休 手応え-2 余白-3 つながり+2</t>
+        </is>
+      </c>
+      <c r="L207" s="6" t="inlineStr">
+        <is>
+          <t>戻るけれど、短い時間で働く</t>
+        </is>
+      </c>
+      <c r="M207" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:出産時に就業 フラグ:育休 お金-3 手応え-4 余白+1 つながり+3</t>
+        </is>
+      </c>
+      <c r="N207" s="6" t="inlineStr">
+        <is>
+          <t>仕事を辞めて、子育てに専念する</t>
+        </is>
+      </c>
+      <c r="O207" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:出産時に就業 フラグ:出産退職 フラグ:子育て専念 キャリア:無職 お金-8 手応え-6 余白+3 つながり+5</t>
+        </is>
+      </c>
+      <c r="P207" s="6" t="n"/>
+      <c r="Q207" s="6" t="inlineStr">
+        <is>
+          <t>第1子のときだけ。出産前に働いていた女性のうち、第1子の出産後も働き続けた人 69.5％（第16回出生動向基本調査、2015〜19年に第1子）</t>
+        </is>
+      </c>
+      <c r="R207" s="6" t="n"/>
+      <c r="S207" s="6" t="n"/>
+      <c r="T207" s="6" t="n"/>
+      <c r="U207" s="6" t="n"/>
+      <c r="V207" s="6" t="n"/>
+      <c r="W207" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="AM207" t="inlineStr">
+        <is>
+          <t>45,24,31</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>E137</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>性別=男;フラグ:出産直後;働き方=会社員|公務員</t>
+        </is>
+      </c>
+      <c r="F208" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>育休</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>人事の書類に「育児休業」の欄があった。
+去年、隣の課の先輩が一か月取っていた。
+戻ってきた先輩の机には、子どもの描いた絵が一枚、増えていた。</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>育休を取る</t>
+        </is>
+      </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:育休 つながり+5 手応え-2 お金-2 余白-2</t>
+        </is>
+      </c>
+      <c r="L208" s="6" t="inlineStr">
+        <is>
+          <t>取らずに、早く帰る日を増やす</t>
+        </is>
+      </c>
+      <c r="M208" s="6" t="inlineStr">
+        <is>
+          <t>つながり+1 余白-3</t>
+        </is>
+      </c>
+      <c r="N208" s="6" t="n"/>
+      <c r="O208" s="6" t="n"/>
+      <c r="P208" s="6" t="n"/>
+      <c r="Q208" s="6" t="inlineStr">
+        <is>
+          <t>第1子のときだけ。男性の育休取得率 30.1％（2023年度 雇用均等基本調査）</t>
+        </is>
+      </c>
+      <c r="R208" s="6" t="n"/>
+      <c r="S208" s="6" t="n"/>
+      <c r="T208" s="6" t="n"/>
+      <c r="U208" s="6" t="n"/>
+      <c r="V208" s="6" t="n"/>
+      <c r="W208" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+      <c r="AM208" t="inlineStr">
+        <is>
+          <t>30,70</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>E138</t>
+        </is>
+      </c>
+      <c r="B209" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>性別=女;フラグ:出産直後</t>
+        </is>
+      </c>
+      <c r="F209" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="6" t="n"/>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>産後</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>産後の体は、自分のものではないみたいに重かった。三か月たって、ようやく階段を一段とばしで上がれた。</t>
+        </is>
+      </c>
+      <c r="J209" s="6" t="n"/>
+      <c r="K209" s="6" t="n"/>
+      <c r="L209" s="6" t="n"/>
+      <c r="M209" s="6" t="n"/>
+      <c r="N209" s="6" t="n"/>
+      <c r="O209" s="6" t="n"/>
+      <c r="P209" s="6" t="inlineStr">
+        <is>
+          <t>健康-3</t>
+        </is>
+      </c>
+      <c r="Q209" s="6" t="n"/>
+      <c r="R209" s="6" t="n"/>
+      <c r="S209" s="6" t="n"/>
+      <c r="T209" s="6" t="n"/>
+      <c r="U209" s="6" t="n"/>
+      <c r="V209" s="6" t="n"/>
+      <c r="W209" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>E139</t>
+        </is>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>選択</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:子育て専念;キャリア=無職;末子の年齢&gt;=3</t>
+        </is>
+      </c>
+      <c r="F210" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G210" s="6" t="n"/>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>また働く</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>子どもを園に送ったあとの帰り道、パートの募集の貼り紙が目に入った。
+「週三日から」の文字を、しばらく眺めていた。</t>
+        </is>
+      </c>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t>パートで働きはじめる</t>
+        </is>
+      </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>フラグ消:子育て専念 キャリア:非正規 お金+4 余白-2 手応え+3 フラグ:転職経験</t>
+        </is>
+      </c>
+      <c r="L210" s="6" t="inlineStr">
+        <is>
+          <t>正社員の仕事を探す</t>
+        </is>
+      </c>
+      <c r="M210" s="6" t="inlineStr">
+        <is>
+          <t>フラグ消:子育て専念 処理:再就職判定</t>
+        </is>
+      </c>
+      <c r="N210" s="6" t="inlineStr">
+        <is>
+          <t>もう少し、家にいる</t>
+        </is>
+      </c>
+      <c r="O210" s="6" t="inlineStr">
+        <is>
+          <t>つながり+2 お金-1</t>
+        </is>
+      </c>
+      <c r="P210" s="6" t="n"/>
+      <c r="Q210" s="6" t="inlineStr">
+        <is>
+          <t>子育てのあと働き方を戻す（女性の就業率は30代後半で底になり、40代で戻る「M字」。労働力調査）</t>
+        </is>
+      </c>
+      <c r="R210" s="6" t="n"/>
+      <c r="S210" s="6" t="n"/>
+      <c r="T210" s="6" t="n"/>
+      <c r="U210" s="6" t="inlineStr">
+        <is>
+          <t>末子の年齢&gt;=6→×1.6／お金&lt;35→×1.5</t>
+        </is>
+      </c>
+      <c r="V210" s="6" t="n"/>
+      <c r="W210" s="6" t="inlineStr">
+        <is>
+          <t>仕事</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>60,15,25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25088,7 +25465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25736,13 +26113,13 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>余白&lt;30;!同級生:美咲=B;!亡:美咲</t>
+          <t>余白&lt;30;!美咲=B;!亡:美咲</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>「疲れてる？」
-帰り際、美咲にそう言われた。看護師の目だった。
+帰り際、美咲にそう言われた。〔美咲=A|C|H〕看護師の目だった。〔それ以外〕昔から、そういうことにいちばん先に気づく人だった。〔/〕
 「大丈夫」と答えた声が、自分の耳にも大丈夫そうに聞こえなかった。</t>
         </is>
       </c>
@@ -28081,6 +28458,1768 @@
         <is>
           <t>「あなたへ」は上から順に条件を見て、最初に合ったもの1つだけ出す。条件が空の行は、どれにも合わなかったときの予備。美咲が欠席するパターン（B）では R35-12 を使わない。
 「名簿」は名簿カードに出す自分のひとこと近況。「あなたへ」と同じく、上から最初に合った1つ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>R25-24</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>健太=D;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>健太は、ジャージの上にジャケットを着て来た。
+「中学の体育。サッカー部の顧問」
+土日がない、と言うわりに、声がいちばん楽しそうだった。</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>R35-24</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>健太=D;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>健太は、県大会の写真を見せて回った。写っているのは、健太ではなく生徒たちだった。
+「俺より、あいつらのほうがうまい」と、なぜか自慢げに言った。</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>R50-24</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>健太=D;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>健太は教頭になっていた。「職員室の電話番だよ」と笑う。
+ジャージではない健太を、初めて見た気がした。</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>R65-24</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>健太=D;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>健太は、再任用で週に三日だけ授業をしていると言った。
+「孫みたいな歳の子に、パスの出し方を教えてる」</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>R25-25</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>健太=E;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>健太は、二十四時間勤務の明けで来たと言った。消防士になっていた。
+「寝てないけど、元気」
+その言い方が、高校のころの朝練のあとと同じだった。</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>R35-25</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>健太=E;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>健太は、救急車に乗っている、と言った。
+「夜中の電話は、だいたい誰かのいちばん悪い日なんだよ」
+焼き鳥を食べる手が、一瞬だけ止まった。</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>R50-25</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>健太=E;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>健太は副署長になっていた。
+「現場に出られないのが、いちばんつらい」
+そう言いながら、非常口の位置を、ちらっと確かめていた。</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/ふつう/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>R65-25</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>健太=E;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>健太は、町内の防災訓練を仕切っていると言った。
+「声が大きいのが、やっと役に立った」</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>R25-26</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>健太=F;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>健太は、営業成績の表彰状の写真を見せた。家を売る仕事だという。
+「人と話すのが仕事って、天職だろ」
+確かに、と全員が思った。</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>R35-26</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>健太=F;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>健太は、駅の向こうにできたマンションを「あれ、半分俺が売った」と言った。
+たぶん、少しだけ盛っていた。</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>R50-26</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>健太=F;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>健太は、駅前に自分の不動産屋を開いていた。
+「この町で家を探すなら、まず俺に聞け」
+名刺の肩書きは、社長だった。</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>R65-26</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>健太=F;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>健太は、店を娘さんに任せたと言った。
+「いまは空き家を見て回る係。この町、空き家ばっかりだよ」
+少しだけ、さびしそうに言った。</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>R25-27</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>健太=G;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>健太は、新車のカタログを鞄に入れて来た。「誰か、車買わない？」
+半分冗談で、半分本気の顔だった。</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>R35-27</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>健太=G;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>健太は、販売店の店長になっていた。
+「月末になると、胃がね」と笑って、ウーロン茶を頼んだ。</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>R50-27</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>健太=G;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>健太は、国道沿いで中古車屋をやっていると言った。
+「売るより、直して長く乗ってもらうほうが好きなんだ」</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>R65-27</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>健太=G;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>健太の店には、まだ健太が立っているらしい。
+「最後の一台を売ったら、やめる。その一台が、なかなか決まらない」</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>R25-28</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>健太=H;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>健太は、地元の会社で営業をしていた。「祭りの実行委員、やらされてる」
+やらされている、と言うわりに、半纏の写真ばかり見せてきた。</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>R35-28</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>健太=H;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>健太は、実家の酒屋を手伝いながら、商店街の祭りを仕切っていた。
+「シャッター、一枚でも開けたいんだよ」</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>R50-28</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>健太=H;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>健太は、市議会議員になっていた。三期目だという。
+同窓会の最中にも、二回、誰かと電話で話していた。</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>R65-28</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>健太=H;!亡:健太</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>健太は、市議会の議長になっていた。
+「乾杯の挨拶、頼む」と幹事に言われて、珍しく短く済ませた。</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:健太/笑顔/左</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>R25-34</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>美咲=D;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>美咲は保育士になっていた。
+「毎日、だれかに鼻水つけられてる」
+そう言って笑う顔が、保健委員のころと同じだった。</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>R35-34</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>美咲=D;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、自分の子どもを、自分の働く保育園に預けていると言った。
+「先生って呼ばれるのと、ママって呼ばれるの、混ざっちゃう」</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>R50-34</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>美咲=D;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、保育園の園長になっていた。
+「卒園生が、もう親になって子どもを連れてくるの」</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>R65-34</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>美咲=D;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、園長を退いて、週に一度、絵本を読みに行っていると言った。
+「声の出し方だけは、まだ負けない」</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>R25-35</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>美咲=E;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>美咲は薬学部を出て、病院の薬剤部にいた。
+「看護師になると思ってたでしょ」と先に言われて、全員が頷いた。</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>R35-35</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>美咲=E;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、調剤薬局で時短で働いていると言った。
+「四時に上がって、保育園に走るの」
+腕時計を、何度か見ていた。</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>R50-35</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>美咲=E;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、商店街に自分の薬局を開いていた。
+「薬の話より、世間話を聞きに来る人のほうが多いの」</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>R65-35</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>美咲=E;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>美咲の薬局は、まだ開いているらしい。
+「血圧の薬、ちゃんと飲んでる？」と聞かれて、何人かが目をそらした。</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>R25-36</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>美咲=F;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、市役所の福祉課にいた。
+「毎日、だれかの家に行ってる」
+仕事の話はそれ以上しなかったけれど、声が少し大人になっていた。</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>R35-36</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>美咲=F;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、子どもの相談の係に移ったと言った。
+「電話が鳴るたびに、背筋が伸びる」</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>R50-36</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>美咲=F;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、福祉課の課長になっていた。
+「ハンコを押す人になっちゃった」と言いながら、誰かの親の介護の話を、ずっと聞いていた。</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/ふつう/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>R65-36</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>美咲=F;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、退職して民生委員をしていると言った。
+「この町のお年寄り、だいたい知り合い」</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>R25-37</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>美咲=G;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、地元の会社で事務をしていた。
+「来年、結婚する」
+そう言うと拍手が起きて、美咲は少しだけ困った顔をした。</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>R35-37</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>美咲=G;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、二人目が生まれたときに会社を辞めたと言った。
+「いまはスーパーのパート。レジ、速いよ」</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>R50-37</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>美咲=G;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、介護の資格を取り直して、ケアマネジャーになっていた。
+「四十過ぎてからの勉強が、いちばん楽しい」</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>R65-37</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>美咲=G;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、まだ現役で、利用者の家を車で回っていると言った。
+「同い年の人の担当になったときは、さすがに考えた」</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>R25-38</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>美咲=H;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、看護師を辞めて医学部を受け直すと言った。
+「悔しい思いを、何度もしたから」
+冗談に聞こえなかったので、誰も笑わなかった。</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>R35-38</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>美咲=H;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、研修医になっていた。三十五歳の研修医。
+「当直の夜は、二十代の子より体がきつい」と笑った。</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>R50-38</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>美咲=H;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、小児科のクリニックを開いていた。
+待合室の絵本は、全部自分で選んだのだという。</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>R65-38</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>美咲=H;!亡:美咲</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>美咲は、まだ町の診療所で診察していると言った。
+「最初に診た子が、自分の子を連れてくるの」</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:美咲/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>R25-44</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>拓海=D;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、電機メーカーで設計をしていると言った。
+何を設計しているのか聞くと、「ねじの、少し上くらいのもの」と答えた。</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>R35-44</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>拓海=D;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、新しい冷蔵庫のチラシを見せた。
+「この、扉のちょうつがい」
+指さす指先が、少しだけ誇らしげだった。</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>R50-44</t>
+        </is>
+      </c>
+      <c r="B153" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>拓海=D;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、開発部の部長になっていた。
+「会議ばっかり。図面を描く時間が、一日に十分もない」</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/ふつう/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>R65-44</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>拓海=D;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、再雇用で若い人に図面を教えていると言った。
+「パソコンじゃなくて、鉛筆で描かせてる」</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>R25-45</t>
+        </is>
+      </c>
+      <c r="B155" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>拓海=E;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、ゲーム会社でプログラムを書いていると言った。
+タイトルを聞くと、何人かが「やってる！」と声を上げた。
+拓海は、聞こえないふりをして、少しだけ笑った。</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>R35-45</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>拓海=E;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、ディレクターになっていた。
+「エンドロールの、上のほうに名前がある」
+誰も最後まで見たことがなかったので、その場で何人かが動画を探した。</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>R50-45</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>拓海=E;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、五人でゲーム会社をやっていると言った。
+「大きいのは作らない。作りたいのだけ作る」</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>R65-45</t>
+        </is>
+      </c>
+      <c r="B158" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>拓海=E;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、ひとりでまだゲームを作っていると言った。
+「完成させたら、終わっちゃう気がして」</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/照れ/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>R25-46</t>
+        </is>
+      </c>
+      <c r="B159" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>拓海=F;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>拓海は来なかった。
+誰かが「家から、あまり出てないらしい」と小声で言った。
+その話は、それ以上続かなかった。</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>R35-46</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>拓海=F;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>拓海が来た。十年ぶりだった。
+「町工場で働いてる。三年目」
+爪の間の黒い油を、少し恥ずかしそうに隠した。</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>R50-46</t>
+        </is>
+      </c>
+      <c r="B161" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>拓海=F;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、旋盤の一級技能士になったと言った。
+「百分の一ミリが、手でわかる」
+あの器用な指は、ちゃんと行き先を見つけていた。</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/ふつう/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>R65-46</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>拓海=F;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、まだ工場で旋盤を回していると言った。
+「社長が、辞めさせてくれない」
+うれしそうに言った。</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/照れ/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>R25-47</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>拓海=G;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、時計店で修理の見習いをしていると言った。
+無口なのは相変わらずで、腕時計の話のときだけ、急に言葉が増えた。</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>R35-47</t>
+        </is>
+      </c>
+      <c r="B164" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>拓海=G;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>拓海の目のまわりに、ルーペの跡が丸く残っていた。
+「一日に三個しか直せない。でも、三個は直せる」</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>R50-47</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>拓海=G;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、自分の工房を開いていた。修理待ちは半年だという。
+誰かが父親の形見の時計を預けると、拓海は両手で受け取った。</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/ふつう/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>R65-47</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>拓海=G;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、まだルーペをのぞいていると言った。
+「時計より先に、こっちの目が止まりそう」</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/笑顔/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>R25-48</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>拓海=H;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、まだ大学院にいた。ロボットの手の研究をしているという。
+「卵をつかめるようになった。割らずに」
+それがどれくらいすごいのか、誰にもわからなかった。</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>R35-48</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>拓海=H;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、三つ目の大学に移ったところだった。
+「任期が切れると、引っ越す」
+段ボールを開けないまま暮らしている、と言った。</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>R50-48</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>拓海=H;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、教授になっていた。
+「研究より、書類を書いてる時間のほうが長い」
+学生の写真を見せるとき、声が少し柔らかくなった。</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/ふつう/右</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>R65-48</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>同級生</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>拓海=H;!亡:拓海</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>拓海は、名誉教授になったと言った。
+「卵、まだ割っちゃうんだよ。ロボットじゃなくて、俺が」</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
+        <is>
+          <t>立ち絵:拓海/照れ/右</t>
         </is>
       </c>
     </row>
@@ -28095,7 +30234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -28193,7 +30332,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>サッカー部。声が大きく、誰とでも話す。商社に入る</t>
+          <t>サッカー部。声が大きく、誰とでも話す</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -28206,10 +30345,8 @@
           <t>海外で生きる</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="E2" s="4" t="n">
+        <v>0.14</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -28273,10 +30410,8 @@
           <t>地元でカフェ</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E3" s="4" t="n">
+        <v>0.14</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -28344,10 +30479,8 @@
           <t>体を壊す</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E4" s="4" t="n">
+        <v>0.14</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -28402,7 +30535,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>保健委員。面倒見がよい。看護師になる</t>
+          <t>保健委員。面倒見がよい</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -28415,10 +30548,8 @@
           <t>病棟で主任に</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="E5" s="4" t="n">
+        <v>0.14</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -28482,10 +30613,8 @@
           <t>結婚して県外へ</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E6" s="4" t="n">
+        <v>0.12</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -28553,10 +30682,8 @@
           <t>親の介護で実家へ</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E7" s="4" t="n">
+        <v>0.1</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -28611,7 +30738,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>パソコン部。無口だが手先が器用。大学を中退する</t>
+          <t>パソコン部。無口だが手先が器用</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -28624,10 +30751,8 @@
           <t>起業組で成功</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E8" s="4" t="n">
+        <v>0.1</v>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
@@ -28695,10 +30820,8 @@
           <t>渡り歩く</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="E9" s="4" t="n">
+        <v>0.17</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -28762,10 +30885,8 @@
           <t>実家の畑を継ぐ</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+      <c r="E10" s="4" t="n">
+        <v>0.1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -28809,6 +30930,947 @@
         </is>
       </c>
       <c r="O10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>健太</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>体育の先生</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>教員二年目。部活の顧問で土日がない</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>県大会に生徒を連れていった</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>中学校の教員</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>中学校の教員（サッカー部顧問）</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>教頭になった。笛を吹く回数が減った</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>再任用で、週三日だけ授業をしている</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>中学校の教頭</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>再任用の講師</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>健太</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>消防士</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>消防学校を出て、署の当番勤務</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>救急隊。夜中の出動が多い</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>消防士</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>救急隊員</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>副署長になった</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>退職して、町内の防災訓練を仕切っている</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>消防署の副署長</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>地域の防災指導員</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>健太</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>家を売る</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>住宅の営業。売上で表彰された</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>支店の所長</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>不動産会社の営業</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>不動産会社の所長</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>独立して、駅前に小さな不動産屋を開いた</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>店は娘に任せて、空き家を見て回る係</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>不動産屋の社長</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>不動産屋の会長</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>健太</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>車を売る</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>車の営業。月末はノルマに追われている</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>販売店の店長</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>自動車販売店の営業</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>自動車販売店の店長</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>独立して、国道沿いで中古車店をやっている</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>まだ店に立っている</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>中古車店の店主</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>中古車店の店主</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>健太</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>町の顔</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>地元の会社で営業。祭りの実行委員</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>実家の酒屋を手伝いながら、商店街の祭りを仕切る</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>地元企業の営業</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>家業の酒屋</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>市議会議員。三期目</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>市議会の議長になった</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>市議会議員</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>市議会議長</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>美咲</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>保育士</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>保育士。毎日、泥だらけ</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>主任保育士。自分の子も同じ園に</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>保育士</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>主任保育士</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>園長になった</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>園長を退いて、絵本の読み聞かせに通う</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>保育園の園長</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>保育園の相談役</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>美咲</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>薬剤師</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>病院の薬剤部で働いている</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>子育てしながら、調剤薬局で時短勤務</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>薬剤師（病院）</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>薬剤師（調剤薬局・時短）</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>商店街で自分の薬局を開いた</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>店の奥で、まだ薬の相談に乗っている</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>薬局の経営者</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>薬局の相談役</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>美咲</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>市役所の福祉課</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>市役所の福祉課。毎日、誰かの家に行く</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>子どもの相談の係に移った</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>市役所（福祉課）</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>市役所（子ども相談）</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>福祉課の課長</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>退職して、民生委員をしている</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>市役所の福祉課長</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>民生委員</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>美咲</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>回り道</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>地元の会社で事務。結婚が決まった</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>出産で会社を辞めて、いまはパート</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>一般事務</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>パート（子育て中）</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>介護の資格を取り直して、ケアマネジャーになった</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>まだ現役で、利用者の家を回っている</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>ケアマネジャー</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>ケアマネジャー</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>美咲</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>医者になる</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>看護師。医学部を受け直すと決めた</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>三十代で医学部を出て、研修医になった</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>看護師</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>研修医</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>小児科のクリニックを開いた</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>町の診療所で、まだ診察している</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>小児科の開業医</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>町の診療所の医師</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>拓海</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>技術者</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>工学部を出て、電機メーカーの設計部</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>設計した部品が、新しい冷蔵庫に入った</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>電機メーカーの技術者</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>電機メーカーの主任技師</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>開発部の部長</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>再雇用で、若手に図面の描き方を教えている</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>開発部の部長</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>再雇用（技術指導）</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>拓海</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>ゲームを作る</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>ゲーム会社でプログラマー</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>ディレクターになった</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>ゲーム会社のプログラマー</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>ゲーム会社のディレクター</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>独立して、五人でゲーム会社をやっている</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>ひとりで、まだゲームを作っている</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>小さなゲーム会社の代表</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>ゲーム作家</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>拓海</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>遅れて歩き出す</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>同窓会には来ない。家から、あまり出ていないらしい</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>就労支援を経て、町工場で働きはじめた</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>町工場の見習い</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>旋盤の一級技能士になった</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>工場で、まだ旋盤を回している</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>町工場の職人</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>町工場の職人（一級技能士）</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>拓海</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>時計職人</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>専門学校を出て、時計店で修理の見習い</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>時計修理の職人</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>時計店の見習い</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>時計修理の職人</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>自分の工房を開いた。修理待ちが半年</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>まだルーペをのぞいている</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>時計修理工房の主</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>時計修理工房の主</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>拓海</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>研究者</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>大学院で、ロボットの手の研究</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>任期つきの研究員。三つ目の大学</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>大学院生</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>大学の研究員（任期付き）</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>教授になった</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>退官して、名誉教授に</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>大学の教授</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>名誉教授</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -28823,7 +31885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28832,6 +31894,7 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28918,6 +31981,11 @@
       <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>学部</t>
+        </is>
+      </c>
+      <c r="R1" s="5" t="inlineStr">
+        <is>
+          <t>女性の割合</t>
         </is>
       </c>
     </row>
@@ -29038,6 +32106,9 @@
       </c>
       <c r="P3" s="6" t="n"/>
       <c r="Q3" s="6" t="n"/>
+      <c r="R3" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -29111,6 +32182,9 @@
           <t>理系×1.5,文系,教育学部</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -29184,6 +32258,9 @@
         </is>
       </c>
       <c r="Q5" s="6" t="n"/>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -29547,6 +32624,9 @@
           <t>理系×2,文系,教育学部</t>
         </is>
       </c>
+      <c r="R12" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -29616,6 +32696,9 @@
       </c>
       <c r="P13" s="6" t="n"/>
       <c r="Q13" s="6" t="n"/>
+      <c r="R13" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -29689,6 +32772,9 @@
           <t>文系,理系,教育学部,薬学部×0.3</t>
         </is>
       </c>
+      <c r="R14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -29766,6 +32852,9 @@
           <t>文系,理系,教育学部,看護・医療</t>
         </is>
       </c>
+      <c r="R15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -29844,6 +32933,9 @@
         <is>
           <t>教育学部×6,文系,理系</t>
         </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
@@ -29914,6 +33006,9 @@
       </c>
       <c r="P17" s="6" t="n"/>
       <c r="Q17" s="6" t="n"/>
+      <c r="R17" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -29992,6 +33087,9 @@
         <is>
           <t>理系×2,文系</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
@@ -30062,6 +33160,9 @@
       </c>
       <c r="P19" s="6" t="n"/>
       <c r="Q19" s="6" t="n"/>
+      <c r="R19" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -30131,6 +33232,9 @@
       </c>
       <c r="P20" s="6" t="n"/>
       <c r="Q20" s="6" t="n"/>
+      <c r="R20" t="n">
+        <v>0.55</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -30204,6 +33308,9 @@
         </is>
       </c>
       <c r="Q21" s="6" t="n"/>
+      <c r="R21" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -30273,6 +33380,9 @@
       </c>
       <c r="P22" s="6" t="n"/>
       <c r="Q22" s="6" t="n"/>
+      <c r="R22" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -30342,6 +33452,9 @@
       </c>
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="n"/>
+      <c r="R23" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -30411,6 +33524,9 @@
       </c>
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="n"/>
+      <c r="R24" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -30484,6 +33600,9 @@
         </is>
       </c>
       <c r="Q25" s="6" t="n"/>
+      <c r="R25" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -30553,6 +33672,9 @@
       </c>
       <c r="P26" s="6" t="n"/>
       <c r="Q26" s="6" t="n"/>
+      <c r="R26" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -30624,6 +33746,9 @@
       </c>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
+      <c r="R27" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -30699,6 +33824,9 @@
           <t>看護・医療</t>
         </is>
       </c>
+      <c r="R28" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -30774,6 +33902,9 @@
           <t>医学部</t>
         </is>
       </c>
+      <c r="R29" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -30849,6 +33980,9 @@
           <t>歯学部</t>
         </is>
       </c>
+      <c r="R30" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -30924,6 +34058,9 @@
           <t>薬学部</t>
         </is>
       </c>
+      <c r="R31" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -30999,6 +34136,9 @@
           <t>教育学部×3,文系</t>
         </is>
       </c>
+      <c r="R32" t="n">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -31073,6 +34213,9 @@
         <is>
           <t>理系×3,医学部×0.1,薬学部×0.2</t>
         </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="34">
@@ -31143,6 +34286,9 @@
       </c>
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n"/>
+      <c r="R34" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -31216,6 +34362,9 @@
         </is>
       </c>
       <c r="Q35" s="6" t="n"/>
+      <c r="R35" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -31285,6 +34434,9 @@
       </c>
       <c r="P36" s="6" t="n"/>
       <c r="Q36" s="6" t="n"/>
+      <c r="R36" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -31354,6 +34506,9 @@
       </c>
       <c r="P37" s="6" t="n"/>
       <c r="Q37" s="6" t="n"/>
+      <c r="R37" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -31423,6 +34578,9 @@
       </c>
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="n"/>
+      <c r="R38" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -31492,6 +34650,9 @@
       </c>
       <c r="P39" s="6" t="n"/>
       <c r="Q39" s="6" t="n"/>
+      <c r="R39" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -31561,6 +34722,9 @@
       </c>
       <c r="P40" s="6" t="n"/>
       <c r="Q40" s="6" t="n"/>
+      <c r="R40" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -31634,6 +34798,9 @@
         </is>
       </c>
       <c r="Q41" s="6" t="n"/>
+      <c r="R41" t="n">
+        <v>0.1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -33371,7 +36538,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="6" t="n">
-        <v>0.08</v>
+        <v>0.096</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
@@ -33397,7 +36564,7 @@
         <v>39</v>
       </c>
       <c r="E67" s="6" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
@@ -33423,7 +36590,7 @@
         <v>49</v>
       </c>
       <c r="E68" s="6" t="n">
-        <v>0.035</v>
+        <v>0.042</v>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
@@ -33449,7 +36616,7 @@
         <v>59</v>
       </c>
       <c r="E69" s="6" t="n">
-        <v>0.025</v>
+        <v>0.03</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
@@ -34066,7 +37233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -34990,6 +38157,162 @@
       <c r="F35" s="6" t="inlineStr">
         <is>
           <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>65歳までに亡くなる（男）</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:死亡@65|全員;性別=男</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>令和6年簡易生命表（男）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>65歳までに亡くなる（女）</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:死亡@65|全員;性別=女</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>令和6年簡易生命表（女）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>50歳で一度も結婚していない（男）</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>!フラグ:結婚経験@50|性別=男</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>2020年国勢調査（50歳時の未婚割合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>50歳で一度も結婚していない（女）</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>!フラグ:結婚経験@50|性別=女</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>2020年国勢調査（50歳時の未婚割合）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>第1子の出産で仕事を辞める女性（出産前に働いていた人のうち）</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:出産退職@50|フラグ:出産時に就業</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>第16回出生動向基本調査（2015〜19年に第1子）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>第1子で育休を取る男性</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:育休@50|性別=男;フラグ:子ども</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>2023年度 雇用均等基本調査（30.1％）。会社員・公務員のみ問う</t>
         </is>
       </c>
     </row>
@@ -35346,7 +38669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -35614,46 +38937,42 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>働き方</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>同い年</t>
+          <t>共働き</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>人口動態統計：どちらが年上でも3歳差までに約7割（内閣府資料）</t>
+          <t>2023年 労働力調査（共働き1,278万世帯・片働き517万世帯）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>働き方</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>1〜3歳上</t>
+          <t>片方が家庭中心</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n">
-        <v>2</v>
-      </c>
+      <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
@@ -35664,261 +38983,475 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>相性</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>1〜3歳下</t>
+          <t>合う</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ゲームの設計（隠れた運命。離婚の起きやすさに影響）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>相性</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>4〜9歳上</t>
+          <t>ふつう</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n">
-        <v>6</v>
-      </c>
+      <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ゲームの設計</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>相性</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>4〜9歳下</t>
+          <t>ずれがある</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n">
-        <v>-6</v>
-      </c>
+      <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ゲームの設計</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>年齢差</t>
+          <t>分担</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>10歳以上離れている</t>
+          <t>分け合う</t>
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n">
-        <v>12</v>
-      </c>
+      <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ゲームの設計（隠れた運命。余白の減り方に影響）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>働き方</t>
+          <t>分担</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>共働き</t>
+          <t>偏る</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>2023年 労働力調査（共働き1,278万世帯・片働き517万世帯）</t>
+          <t>ゲームの設計</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>働き方</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>片方が家庭中心</t>
+          <t>同い年</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>相性</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>合う</t>
+          <t>1〜3歳上</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
+        <v>36</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>ゲームの設計（隠れた運命。離婚の起きやすさに影響）</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>相性</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>ふつう</t>
+          <t>4〜9歳上</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>6</v>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>ゲームの設計</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>相性</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>ずれがある</t>
+          <t>10歳以上離れている</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>ゲームの設計</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>分担</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>分け合う</t>
+          <t>1〜3歳下</t>
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-2</v>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>ゲームの設計（隠れた運命。余白の減り方に影響）</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>分担</t>
+          <t>年齢差</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>偏る</t>
+          <t>4〜9歳下</t>
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
+        <v>4.5</v>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-6</v>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>ゲームの設計</t>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>10歳以上離れている</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>1〜3歳下</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>4〜9歳下</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>10歳以下離れている</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>1〜3歳上</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>4〜9歳上</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>年齢差</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>10歳以下離れている</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>性別=男</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>人口動態統計（初婚どうしの夫婦の年齢差：夫が年上 約56％、同い年 約21％、妻が年上 約23％）からの推計</t>
         </is>
       </c>
     </row>

--- a/dosokai-life/data/events.xlsx
+++ b/dosokai-life/data/events.xlsx
@@ -11235,7 +11235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM210"/>
+  <dimension ref="A1:AM215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17096,7 +17096,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>フラグ:祖父母の訃報直後</t>
+          <t>フラグ:祖父母の訃報直後;!フラグ:祖父母を見送った</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
@@ -17110,9 +17110,10 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>祖父母の一人が亡くなった。
+          <t>{祖父母}が亡くなった。
 棺の中の顔は、思っていたより小さかった。
-帰りの車で、子どものころにもらったお年玉の袋の柄を、なぜか思い出した。</t>
+帰りの車で、子どものころにもらったお年玉の袋の柄を、なぜか思い出した。〔残っている祖父母の数=0〕
+これで、祖父母はみんないなくなった。〔/〕</t>
         </is>
       </c>
       <c r="J85" s="6" t="n"/>
@@ -17123,12 +17124,12 @@
       <c r="O85" s="6" t="n"/>
       <c r="P85" s="6" t="inlineStr">
         <is>
-          <t>つながり+1 余白-2</t>
+          <t>フラグ:祖父母を見送った つながり+1 余白-2</t>
         </is>
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
-          <t>祖父母の寿命は最初に決まっている（隠れた運命）</t>
+          <t>祖父母の訃報は、最初の一人と最後の一人だけカードにする（あいだは一行）</t>
         </is>
       </c>
       <c r="R85" s="6" t="n"/>
@@ -17136,7 +17137,11 @@
       <c r="T85" s="6" t="n"/>
       <c r="U85" s="6" t="n"/>
       <c r="V85" s="6" t="n"/>
-      <c r="W85" s="6" t="n"/>
+      <c r="W85" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -25451,6 +25456,303 @@
       <c r="AM210" t="inlineStr">
         <is>
           <t>60,15,25</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>E307</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:祖父母の訃報直後;経過:祖父母を見送った&gt;=1;残っている祖父母の数&gt;=1;亡くなった祖父母=母方の祖父|父方の祖父;子ども数=0</t>
+        </is>
+      </c>
+      <c r="F211" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="6" t="n"/>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>祖父</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>{祖父母}の葬儀で、親戚のおじさんたちが知らない昔の話をしていた。祖父にも若いころがあったのだと、初めて思った。</t>
+        </is>
+      </c>
+      <c r="J211" s="6" t="n"/>
+      <c r="K211" s="6" t="n"/>
+      <c r="L211" s="6" t="n"/>
+      <c r="M211" s="6" t="n"/>
+      <c r="N211" s="6" t="n"/>
+      <c r="O211" s="6" t="n"/>
+      <c r="P211" s="6" t="inlineStr">
+        <is>
+          <t>余白-1</t>
+        </is>
+      </c>
+      <c r="Q211" s="6" t="n"/>
+      <c r="R211" s="6" t="n"/>
+      <c r="S211" s="6" t="n"/>
+      <c r="T211" s="6" t="n"/>
+      <c r="U211" s="6" t="n"/>
+      <c r="V211" s="6" t="n"/>
+      <c r="W211" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>E308</t>
+        </is>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D212" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:祖父母の訃報直後;経過:祖父母を見送った&gt;=1;残っている祖父母の数&gt;=1;亡くなった祖父母=母方の祖母|父方の祖母;子ども数=0</t>
+        </is>
+      </c>
+      <c r="F212" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="6" t="n"/>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>祖母</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>{祖父母}が亡くなった。形見分けで、使いかけの毛糸玉をひとつもらった。</t>
+        </is>
+      </c>
+      <c r="J212" s="6" t="n"/>
+      <c r="K212" s="6" t="n"/>
+      <c r="L212" s="6" t="n"/>
+      <c r="M212" s="6" t="n"/>
+      <c r="N212" s="6" t="n"/>
+      <c r="O212" s="6" t="n"/>
+      <c r="P212" s="6" t="inlineStr">
+        <is>
+          <t>余白-1</t>
+        </is>
+      </c>
+      <c r="Q212" s="6" t="n"/>
+      <c r="R212" s="6" t="n"/>
+      <c r="S212" s="6" t="n"/>
+      <c r="T212" s="6" t="n"/>
+      <c r="U212" s="6" t="n"/>
+      <c r="V212" s="6" t="n"/>
+      <c r="W212" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>E309</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:祖父母の訃報直後;経過:祖父母を見送った&gt;=1;残っている祖父母の数&gt;=1;子ども数&gt;=1</t>
+        </is>
+      </c>
+      <c r="F213" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="6" t="n"/>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>曾祖父母</t>
+        </is>
+      </c>
+      <c r="I213" s="6" t="inlineStr">
+        <is>
+          <t>{祖父母}の葬儀で、子どもが初めて喪服を着た。焼香の順番を、小さな声で何度も聞いてきた。</t>
+        </is>
+      </c>
+      <c r="J213" s="6" t="n"/>
+      <c r="K213" s="6" t="n"/>
+      <c r="L213" s="6" t="n"/>
+      <c r="M213" s="6" t="n"/>
+      <c r="N213" s="6" t="n"/>
+      <c r="O213" s="6" t="n"/>
+      <c r="P213" s="6" t="inlineStr">
+        <is>
+          <t>余白-1 つながり+1</t>
+        </is>
+      </c>
+      <c r="Q213" s="6" t="n"/>
+      <c r="R213" s="6" t="n"/>
+      <c r="S213" s="6" t="n"/>
+      <c r="T213" s="6" t="n"/>
+      <c r="U213" s="6" t="n"/>
+      <c r="V213" s="6" t="n"/>
+      <c r="W213" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>E313</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>一行</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:祖父母の訃報直後;経過:祖父母を見送った&gt;=1;残っている祖父母の数&gt;=1;!亡くなった祖父母=母方の祖父|父方の祖父;!亡くなった祖父母=母方の祖母|父方の祖母;子ども数=0</t>
+        </is>
+      </c>
+      <c r="F214" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="6" t="n"/>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>二人</t>
+        </is>
+      </c>
+      <c r="I214" s="6" t="inlineStr">
+        <is>
+          <t>同じ年に、{祖父母}を見送った。二度目の葬儀では、数珠の持ち方を、もう誰にも聞かなかった。</t>
+        </is>
+      </c>
+      <c r="J214" s="6" t="n"/>
+      <c r="K214" s="6" t="n"/>
+      <c r="L214" s="6" t="n"/>
+      <c r="M214" s="6" t="n"/>
+      <c r="N214" s="6" t="n"/>
+      <c r="O214" s="6" t="n"/>
+      <c r="P214" s="6" t="inlineStr">
+        <is>
+          <t>余白-2</t>
+        </is>
+      </c>
+      <c r="Q214" s="6" t="n"/>
+      <c r="R214" s="6" t="n"/>
+      <c r="S214" s="6" t="n"/>
+      <c r="T214" s="6" t="n"/>
+      <c r="U214" s="6" t="n"/>
+      <c r="V214" s="6" t="n"/>
+      <c r="W214" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>E314</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="inlineStr">
+        <is>
+          <t>運命</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D215" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:祖父母の訃報直後;経過:祖父母を見送った&gt;=1;残っている祖父母の数=0</t>
+        </is>
+      </c>
+      <c r="F215" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="6" t="n"/>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>最後の祖父母</t>
+        </is>
+      </c>
+      <c r="I215" s="6" t="inlineStr">
+        <is>
+          <t>{祖父母}が亡くなって、祖父母はみんないなくなった。
+お盆に帰る家が、ひとつ減った。
+法事のときに撮る集合写真の、いちばん上の段が空いた。</t>
+        </is>
+      </c>
+      <c r="J215" s="6" t="n"/>
+      <c r="K215" s="6" t="n"/>
+      <c r="L215" s="6" t="n"/>
+      <c r="M215" s="6" t="n"/>
+      <c r="N215" s="6" t="n"/>
+      <c r="O215" s="6" t="n"/>
+      <c r="P215" s="6" t="inlineStr">
+        <is>
+          <t>つながり+1 余白-2</t>
+        </is>
+      </c>
+      <c r="Q215" s="6" t="n"/>
+      <c r="R215" s="6" t="n"/>
+      <c r="S215" s="6" t="n"/>
+      <c r="T215" s="6" t="n"/>
+      <c r="U215" s="6" t="n"/>
+      <c r="V215" s="6" t="n"/>
+      <c r="W215" s="6" t="inlineStr">
+        <is>
+          <t>家族</t>
         </is>
       </c>
     </row>

--- a/dosokai-life/data/events.xlsx
+++ b/dosokai-life/data/events.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人物" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配偶者" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="くじ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="つなぎ" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -882,6 +883,34 @@
       <c r="A64" t="inlineStr">
         <is>
           <t>同級生シート：一人8通りの人生（A〜H）。同窓会シートの「健太=D」のような行で、それぞれの様子を書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>■ 同じ文章をくり返さないしくみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>一行の出来事は、一生に一度だけ。本文を「〔次〕」で区切ると、2回目・3回目は次の文章になる（一行なら、その回数まで起きる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>カード（選択・運命）は何度でも起きる。〔次〕で2回目以降の文章を書いておくと、同じ文章にならない（使い切ったら最後の文章）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>つなぎシート：毎年のはじめに出る一文。一生に一度ずつ使う。「優先」に○があり条件に合う行（景気が変わった年など）を先に選ぶ</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1705,10 @@
       <c r="J9" s="6" t="inlineStr">
         <is>
           <t>税理士の事務所で、親が残したものの一覧を見せてもらった。
-知らなかった口座が、二つあった。</t>
+知らなかった口座が、二つあった。
+〔次〕
+もう一人の親の遺品を整理していたら、通帳が一冊出てきた。
+知らない名前の定期預金が、満期のまま眠っていた。</t>
         </is>
       </c>
       <c r="K9" s="6" t="n"/>
@@ -11221,6 +11253,2027 @@
       <c r="AA123" s="6" t="inlineStr">
         <is>
           <t>くじ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G107"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>年齢(から)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>年齢(まで)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>条件</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>文章</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>B001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n"/>
+      <c r="C2" s="6" t="n"/>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>景気=不況;前年の景気=好況|ふつう</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>駅前の居酒屋が、ひとつ閉まった。景気が悪くなってきたらしい。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>景気が悪くなった年だけ優先。回復・好況の文は、その年に選ばれることもある、くらいにしている</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>B002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="6" t="n"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>景気=不況;前年の景気=好況|ふつう</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>ニュースで「景気後退」という言葉を聞くようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>B003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>景気=不況;前年の景気=好況|ふつう</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>コンビニの棚の値札が、少しずつ書き換わっていった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>B004</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>景気=ふつう|好況;前年の景気=不況|大不況</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>駅前に、新しい店の工事の囲いが立った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>B005</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>景気=ふつう|好況;前年の景気=不況|大不況</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>求人のチラシが、また郵便受けに入るようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>B006</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>景気=ふつう|好況;前年の景気=不況|大不況</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>暗いニュースの割合が、少しだけ減った気がした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>B007</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>景気=好況;前年の景気=ふつう</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>街に、新しいビルのクレーンが増えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>B008</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>景気=好況;前年の景気=ふつう</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>忘年会の二次会が、なかなか終わらない年だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>B009</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>景気=好況;前年の景気=ふつう</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>百貨店の初売りに、長い列ができていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>B101</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>元日の朝、近所の神社で甘酒をもらった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>B102</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>年賀状が、去年より三枚減った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>B103</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>その冬は、雪がほとんど降らなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>B104</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>大雪で、電車が一日止まった冬だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>B105</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>春が来るのが、少し早い年だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>B106</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>桜が、入学式の前に散ってしまった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>B107</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>梅雨が、なかなか明けなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>記録的に暑い夏だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>B109</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>夏祭りの夜、どこかの家の風鈴がずっと鳴っていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>B110</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>台風が三つ続けて来た秋だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>B111</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>金木犀の匂いで、秋が来たのを知った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>B112</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>その年いちばん流行った歌を、最後まで覚えられなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>B113</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>スマホを新しくした。写真を移すのに、一晩かかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>B114</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>近所に新しいコンビニができた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>B115</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>よく行っていた本屋が閉店した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>B116</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>初詣のおみくじは、小吉だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>初詣のおみくじは、大吉だった。何に使えばいいのか、わからなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>B118</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>冬至の夜、ゆず湯に入った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>B119</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>近所の空き地に、家が三軒建った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>B120</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>駅の改札が新しくなって、しばらく迷った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>B121</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>テレビで、オリンピックの中継を見た。知らない競技のルールに、少し詳しくなった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>B122</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>選挙の投票所は、母校の体育館だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>B123</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>電気代の請求書を、二度見した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>B124</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>近所の猫が、いつのまにか見えなくなった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>B125</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>大きな月が出ていた夜、誰かに見せたくて写真を撮った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>B126</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>流星群のニュースを見て、ベランダに出た。一つだけ見えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>B127</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>町内会の回覧板が、また回ってきた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>B128</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>古いアルバムを開いたら、半日つぶれた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>B129</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>地震で、本棚の上の箱が落ちた。それだけで済んだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>B130</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>日曜日の朝、目覚ましなしで起きられた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>B131</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>ふるさと納税の返礼品で、冷凍庫がいっぱいになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>B132</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>年末の大掃除で、なくしたと思っていた鍵が出てきた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>B133</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>駅のホームで高校の制服を見かけて、少し目で追った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>B134</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>財布を新しくした。前の財布のレシートを捨てるのに、少し時間がかかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>B135</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>夜、遠くで花火の音がした。見には行かなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>B136</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>近所の小学校から、運動会の練習の音楽が聞こえていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>B137</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>傘を三本なくした年だった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>B138</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>冷蔵庫が壊れて、新しいのを買った。思ったより静かだった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>B139</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>寝る前に読む本の種類が、少し変わった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>B140</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>家の近くの道に、新しい信号ができた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>B141</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>年末、子どものころテレビで見ていた人の訃報を知った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>B142</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>大きな地震のニュースを、遠い町のこととして見ていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>B143</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>インフルエンザで一週間寝込んだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>B144</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>献血に行った。カードの記録が、ひとつ増えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>B145</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>朝、窓の外に雪が積もっていた。子どものころほど、うれしくはなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>B146</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>久しぶりに、手紙を書いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>B147</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>小さな観葉植物を、枯らさずに一年もたせた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>B148</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>眠れない夜に、ラジオを聴いた。知らない町の天気予報が流れていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>B149</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>使っていないポイントカードを、まとめて捨てた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>B150</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>誕生日に、思っていたより多くのメッセージが届いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>B201</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>知らない駅の名前を、少しずつ覚えていった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>B202</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>夜中のファミレスで、ドリンクバーを五往復した。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>B203</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>免許を取った。初めての高速道路で、ハンドルを握る手が汗ばんだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>B204</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>地元の友達のSNSが、少しずつ知らない景色になっていった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>B205</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n"/>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>成人式の写真が、実家の玄関に飾られた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>B301</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D66" s="6" t="n"/>
+      <c r="E66" s="6" t="n"/>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>友達の結婚式が、三回あった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>B302</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D67" s="6" t="n"/>
+      <c r="E67" s="6" t="n"/>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>ご祝儀袋を、まとめて五枚買った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>B303</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>引っ越しの段ボールを一つ開けないまま、一年が過ぎた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>B304</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>健康診断の結果を、初めて真剣に読んだ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>B305</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>!キャリア=学生|無職</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>後輩ができた。教えるほうが、ずっと難しかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>B401</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D71" s="6" t="n"/>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>白髪を一本見つけた。抜くかどうか、少し迷った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>B402</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C72" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n"/>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>同級生の名前を、地元のニュースで見かけた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>B403</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>老眼鏡を、こっそり買った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>B404</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C74" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D74" s="6" t="n"/>
+      <c r="E74" s="6" t="n"/>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>夜更かしが、次の日にこたえるようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>B405</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>流行りの言葉を、若い人に教えてもらった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>B501</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>「年賀状は今年で最後にします」という葉書が届いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>B502</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D77" s="6" t="n"/>
+      <c r="E77" s="6" t="n"/>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>膝が、天気を教えてくれるようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>B503</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C78" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>同窓会の幹事から、住所の確認の葉書が来た。</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>B504</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n"/>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>昔よく聴いた歌が、懐かしの歌の番組で流れていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>B505</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>フラグ:孫</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>孫の運動会のために、ビデオカメラの使い方を覚えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>B506</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>働き方=会社員|公務員</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>定年まであと何年か、指を折って数えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>B507</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="C82" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>朝のラジオ体操に、顔を出すようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>B601</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n"/>
+      <c r="C83" s="6" t="n"/>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>地域=都市</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n"/>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>満員電車で、知らない人の肩に寄りかかられた。そのまま二駅、動けなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>B602</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>地域=都市</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="n"/>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>ビルの隙間から見える空が、少しだけ広くなった。向かいのビルが取り壊されたらしい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>B603</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>地域=地元</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n"/>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>地元の商店街で、同級生の親に声をかけられた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>B604</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>地域=地元</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="n"/>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>田んぼに水が張られて、夜はカエルの声がにぎやかだった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>B605</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>地域=移住先</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>移住先の言葉の訛りが、少しうつった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>B606</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>地域=海外</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="n"/>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>日本の正月番組を、ネットで少しだけ見た。</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>B607</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>住まい=持ち家</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>庭の木が、去年より少し大きくなった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>B608</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>住まい=持ち家</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="n"/>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>家の外壁に、小さなひびを見つけた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>B609</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>住まい=実家</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="n"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>自分の部屋の本棚に、まだ高校の教科書が並んでいた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>B610</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>住まい=賃貸</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>隣の部屋の人が、引っ越していった。最後まで顔を知らなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>B611</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>パートナー=既婚</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="n"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>パートナーと同じ番組を見て、同じところで笑った。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>B612</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>パートナー=既婚;結婚年数&gt;=5</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>結婚記念日を、二人とも忘れていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>B613</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="6" t="n"/>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>パートナー=交際中</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="n"/>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>二人で行く店が、一つ増えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>B614</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>パートナー=なし</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="n"/>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>一人で行く店が、一つ増えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>B615</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="n"/>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>子ども数&gt;=1;末子の年齢&lt;=5</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="n"/>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>子どもの寝顔を見ているうちに、自分も寝てしまった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>B616</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>子ども数&gt;=1;末子の年齢&lt;=6</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>公園の砂場で、日曜日が半分終わった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>B617</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n"/>
+      <c r="C99" s="6" t="n"/>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>末子の年齢&gt;=7;末子の年齢&lt;=12</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="n"/>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>子どもの算数の宿題が、意外と解けなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>B618</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>長子の年齢&gt;=13;長子の年齢&lt;=18</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="n"/>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>子どもの背が、自分を追い越しそうになっていた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>B619</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>長子の年齢&gt;=19</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>子どもからの連絡は、スタンプひとつだった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>B620</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>父=健在;父の年齢&gt;=75</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="n"/>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>父の歩く速さが、少しゆっくりになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>B621</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>母=健在;母の年齢&gt;=75</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>母が電話で、同じ話を二回するようになった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>B622</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>父=亡</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>父の好きだった銘柄の酒を、店で見かけた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>B623</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n"/>
+      <c r="C105" s="6" t="n"/>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>母=亡</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="n"/>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>母の字で書かれたレシピを、台所の引き出しで見つけた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>B624</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>性別=女</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="n"/>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>夜中に急に暑くなって、目が覚めることが増えた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>B625</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="6" t="n"/>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>キャリア=引退</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="n"/>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>平日の昼のスーパーが、こんなに混んでいるとは知らなかった。</t>
         </is>
       </c>
     </row>
@@ -12617,7 +14670,22 @@
 店主が、何も言わずに二人分のお茶を出すようになった。
 「そろそろ、ちゃんと考えない？」と言われたのは、帰りの信号待ちだった。〔/〕〔フラグ:結婚を保留〕前に「まだ決められない」と答えてから、二年がたった。
 パートナーは、そのことを一度も責めなかった。
-誕生日の夜、ケーキのろうそくを吹き消したあとで、「もう一度だけ聞くね」と前置きされた。〔/〕</t>
+誕生日の夜、ケーキのろうそくを吹き消したあとで、「もう一度だけ聞くね」と前置きされた。〔/〕
+〔次〕
+〔!フラグ:結婚を保留〕日曜日の朝、パートナーが二人分のコーヒーを淹れながら言った。
+「一緒に住む部屋、そろそろ探さない？」
+マグカップの湯気の向こうで、少し照れた顔をしていた。〔それ以外〕「待ってって言われてから、ずっと考えてた」
+パートナーは、区役所でもらってきた書類を一枚、テーブルに置いた。〔/〕
+〔次〕
+〔!フラグ:結婚を保留〕帰りの電車で、パートナーが窓の外を見たまま言った。
+「このまま、ずっと一緒にいるのかなって、思ってる」
+次の駅に着くまで、どちらも何も言わなかった。〔それ以外〕「これで最後にするね」とパートナーは言った。
+責める声ではなかった。それが、かえってこたえた。〔/〕
+〔次〕
+〔!フラグ:結婚を保留〕パートナーの親に、初めて会った。
+帰りの車の中で、「どうだった？」と聞かれた。
+答えるかわりに、「この先のこと、ちゃんと話そうか」と言った。〔それ以外〕パートナーは、何も聞かなくなった。
+聞かれないことが、いちばんの問いかけだった。〔/〕</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -12712,8 +14780,9 @@
 「お二人とも、元気ですよ」
 二人分の泣き声が、廊下の端まで聞こえていた。〔/〕〔!フラグ:双子直後;子ども数=1;性別=女〕長い夜が明けて、胸の上に、熱いかたまりがのせられた。
 握り返される力の強さに、泣きながら笑ってしまった。〔/〕〔!フラグ:双子直後;子ども数=1;性別=男〕生まれてきた子の手は、思っていたより熱かった。
-握り返される力の強さに、意味もなく笑ってしまった。〔/〕〔!フラグ:双子直後;子ども数&gt;=2〕上の子が、新しく来た家族の小さな足を、こわごわと指でつついた。
-「ちっちゃい」と言って、自分の手と見比べていた。〔/〕</t>
+握り返される力の強さに、意味もなく笑ってしまった。〔/〕〔!フラグ:双子直後;子ども数=2〕上の子が、新しく来た家族の小さな足を、こわごわと指でつついた。
+「ちっちゃい」と言って、自分の手と見比べていた。〔/〕〔!フラグ:双子直後;子ども数&gt;=3〕上の子たちが、新しく来た家族を順番に抱っこした。
+いちばん下だった子が、急に年上の顔になった。〔/〕</t>
         </is>
       </c>
       <c r="J19" s="4" t="n"/>
@@ -12951,7 +15020,16 @@
         <is>
           <t>テレビの右上に、赤い数字が並んでいた。
 アナウンサーの「過去最悪」という言葉が、その週だけで何度も繰り返された。
-自分の財布の中身は何も変わっていないのに、なぜか寒かった。</t>
+自分の財布の中身は何も変わっていないのに、なぜか寒かった。
+〔次〕
+ニュースの画面の端に、また見たことのない数字が並んだ。
+前のときを覚えている人ほど、黙っていた。
+〔次〕
+また、大きな不況が来た。
+若い人たちが青い顔をしているのを見て、自分も昔、あんな顔をしていたのだろうと思った。
+〔次〕
+店のシャッターに、「長い間ありがとうございました」の貼り紙が並んだ。
+不況の数え方を、もう覚えてしまった自分がいた。</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr"/>
@@ -14468,7 +16546,16 @@
         <is>
           <t>「次の更新は、ありません」
 担当者は、それを伝える係にすぎない人の顔をしていた。
-ロッカーの名札を外すと、下にもう一枚、前の人の名札が貼られていた。</t>
+ロッカーの名札を外すと、下にもう一枚、前の人の名札が貼られていた。
+〔次〕
+「今回で、契約は終わりになります」
+二度目なので、前ほど驚かなかった。驚かなかったことに、少しだけ驚いた。
+〔次〕
+契約の終わりを伝えるメールは、三行だった。
+最後の行の「今までありがとうございました」だけ、少し字が大きかった。
+〔次〕
+また、更新はなかった。
+帰りに寄ったコンビニで、店員募集の貼り紙を、しばらく見ていた。</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
@@ -14663,7 +16750,13 @@
       <c r="I49" s="4" t="inlineStr">
         <is>
           <t>朝、駅の階段の途中で、手すりが急に遠くなった。
-気がついたときには、知らない人の上着が自分の頭の下にあった。</t>
+気がついたときには、知らない人の上着が自分の頭の下にあった。
+〔次〕
+会議の途中で、資料の文字がにじんで読めなくなった。
+次に見たのは、白い天井だった。
+〔次〕
+夜中、胸のあたりが急に重くなって、自分で救急車を呼んだ。
+住所を言う声が、他人の声みたいだった。</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
@@ -14732,7 +16825,21 @@
         <is>
           <t>目覚ましを三回止めた。
 カーテンの隙間から、いつもと同じ光が入ってくる。
-その光が、今日はやけに重い。</t>
+その光が、今日はやけに重い。
+〔次〕
+日曜日が、天井を見ているうちに終わった。
+夕方、洗濯物を取り込んだことだけが、その日の出来事だった。
+〔次〕
+歯みがきの途中で、手が止まった。
+鏡の中の顔が、何かを待っているように見えた。
+〔次〕
+休みの日、パジャマのまま夕方になった。
+冷蔵庫を開けて、何も取らずに閉めた。
+〔次〕
+好きだったはずの音楽を流しても、何も聞こえてこない朝だった。
+〔次〕
+電車を一本見送って、また一本見送った。
+ホームのベンチから、なかなか立ち上がれなかった。</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
@@ -14808,7 +16915,16 @@
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>{出会いの場面}
-〔年齢&gt;=40〕この歳になって、と思った。思ったけれど、悪くはなかった。〔それ以外〕帰り道、もう一度話したいと思っている自分に気づいた。〔/〕</t>
+〔年齢&gt;=40〕この歳になって、と思った。思ったけれど、悪くはなかった。〔それ以外〕帰り道、もう一度話したいと思っている自分に気づいた。〔/〕
+〔次〕
+{出会いの場面}
+前の恋のことを、少しだけ思い出した。それから、目の前の人のことを考えた。
+〔次〕
+{出会いの場面}
+もう、こういうことはないと思っていた。
+〔次〕
+{出会いの場面}
+家に帰ってから、もう一度その人の名前を声に出してみた。</t>
         </is>
       </c>
       <c r="J51" s="6" t="n"/>
@@ -14930,7 +17046,16 @@
         <is>
           <t>「少し、距離を置きたい」
 その言葉を聞いたのは、いつもの店の、いつもの席だった。
-店主が気をきかせて、注文を取りに来なかった。</t>
+店主が気をきかせて、注文を取りに来なかった。
+〔次〕
+「このままでいいのか、わからなくなった」
+パートナーは、スマホの画面を伏せたまま言った。
+〔次〕
+既読がついてから返事が来るまで、三日かかった。
+四日目の朝、「話したいことがある」と届いた。
+〔次〕
+「好きな人ができた」
+パートナーは、謝るより先にそう言った。</t>
         </is>
       </c>
       <c r="J53" s="6" t="inlineStr">
@@ -15062,7 +17187,10 @@
         <is>
           <t>夕食のあと、パートナーが食器を洗いながら、背中越しに言った。
 「もう一人、考えてる？」
-洗い場の水の音が、しばらく続いた。</t>
+洗い場の水の音が、しばらく続いた。
+〔次〕
+「もう一人、どうする？」
+冗談めかした声だったけれど、目は笑っていなかった。</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
@@ -15197,7 +17325,10 @@
       <c r="I57" s="6" t="inlineStr">
         <is>
           <t>子どもの部屋のドアが、閉まっている時間のほうが長くなった。
-夕食の席で話しかけると、「別に」とだけ返ってきた。</t>
+夕食の席で話しかけると、「別に」とだけ返ってきた。
+〔次〕
+下の子の部屋のドアも、閉まるようになった。
+二度目なのに、慣れることはなかった。</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
@@ -15278,7 +17409,13 @@
         <is>
           <t>子どもが、進路希望の紙を食卓に置いた。
 第一希望の欄に、県外の大学の名前が書いてあった。
-学費の欄は、まだ空いていた。</t>
+学費の欄は、まだ空いていた。
+〔次〕
+下の子も、進路の紙を持ってきた。
+上の子のときより、紙の折り目がきっちりしていた。
+〔次〕
+末の子が、進路の紙を食卓に置いた。
+上の子たちのときと同じペンで、同じ欄に名前を書いた。</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -15535,7 +17672,14 @@
         <is>
           <t>「話がある」とパートナーが言った。
 テーブルの上に、二人分の湯呑みが並んでいた。
-どちらも、しばらく手をつけなかった。</t>
+どちらも、しばらく手をつけなかった。
+〔次〕
+夜中、台所の明かりがついていた。
+パートナーが、一人でお茶を飲んでいた。
+「眠れなくて。少し、話せる？」
+〔次〕
+旅行の計画を立てていたはずが、気づけば、ずっと黙っていた。
+「ねえ、私たち、このままでいいのかな」</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
@@ -16154,7 +18298,16 @@
         <is>
           <t>日曜日のモデルハウスは、どの部屋も新しい木の匂いがした。
 営業の人が、月々の返済額を電卓で見せてくれた。
-家賃と、そんなに変わらない数字だった。三十五年という数字を除けば。</t>
+家賃と、そんなに変わらない数字だった。三十五年という数字を除けば。
+〔次〕
+郵便受けに、新築マンションのチラシが入っていた。
+間取り図の広さを、今の部屋と指で比べた。
+〔次〕
+中古の一軒家の内見に行った。
+柱に、前の住人の子どもがつけた背くらべの傷が、そのまま残っていた。
+〔次〕
+知り合いが家を建てたと聞いて、週末、住宅展示場に寄ってみた。
+風船を配る係の人が、子どもより先にこちらに笑いかけた。</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
@@ -16916,7 +19069,12 @@
         <is>
           <t>〔災害リスク=高〕夜中に、家が横から殴られたように揺れた。〔それ以外〕何日も降り続いた雨で、川の水位が堤防のすぐ下まで来た。〔/〕
 朝のニュースは、自分の住んでいる町の名前ばかりを繰り返していた。
-〔フラグ:自宅被害直後〕家の中は、自分の家だとわからないほどだった。〔それ以外〕自分の家は、なんとか無事だった。〔/〕</t>
+〔フラグ:自宅被害直後〕家の中は、自分の家だとわからないほどだった。〔それ以外〕自分の家は、なんとか無事だった。〔/〕
+〔次〕
+〔災害リスク=高〕また、大きく揺れた。
+前のときに買った懐中電灯が、ちゃんと点いた。〔それ以外〕また、川があふれた。
+前のときに覚えた避難所までの道を、暗い中で歩いた。〔/〕
+町の名前が、またニュースに出た。</t>
         </is>
       </c>
       <c r="J82" s="6" t="n"/>
@@ -16980,7 +19138,10 @@
       <c r="I83" s="6" t="inlineStr">
         <is>
           <t>電気が戻るまでに四日かかった。
-避難所の体育館では、毛布の数が足りていなかった。</t>
+避難所の体育館では、毛布の数が足りていなかった。
+〔次〕
+片づけのボランティアの人たちが、泥だらけの長靴で帰っていった。
+前のときより、手順を知っている人が増えていた。</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
@@ -17796,7 +19957,19 @@
         <is>
           <t>スマホに、転職サイトから通知が届いた。
 〈あなたの経験を活かせる求人が三件あります〉
-昼休み、通知を消さずに、しばらく眺めていた。</t>
+昼休み、通知を消さずに、しばらく眺めていた。
+〔次〕
+昼休み、同期が「辞めることにした」と言った。
+その夜、自分も転職サイトのアプリを、もう一度開いた。
+〔次〕
+知らない会社の人から、「一度お話を」というメッセージが届いた。
+肩書きの横に、自分の名前が正しい漢字で書かれていた。
+〔次〕
+取引先の人に、帰り際「うちに来ない？」と小声で言われた。
+冗談のような顔をしていたけれど、名刺の裏に携帯の番号が書いてあった。
+〔次〕
+久しぶりに、転職サイトから通知が来た。
+登録したことさえ、忘れかけていた。</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
@@ -18671,7 +20844,19 @@
       <c r="I108" s="6" t="inlineStr">
         <is>
           <t>ハローワークの番号札は、六十八番だった。
-呼ばれるまでの一時間、求人票をめくり続けた。</t>
+呼ばれるまでの一時間、求人票をめくり続けた。
+〔次〕
+ハローワークの窓口の人は、前と同じ人だった。
+「今日は、少し条件を広げてみましょうか」
+〔次〕
+求人票の「未経験歓迎」の文字を、指でなぞった。
+家に帰ってから、履歴書の写真を撮り直した。
+〔次〕
+職業訓練の案内を、待合の椅子でめくった。
+「三か月で、資格が取れます」
+〔次〕
+ハローワークの帰りに、公園のベンチで缶コーヒーを飲んだ。
+平日の昼の公園は、思っていたより人が多かった。</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
@@ -24027,7 +26212,10 @@
       <c r="I190" s="6" t="inlineStr">
         <is>
           <t>育休が終わる日が近づいてきた。
-役所の窓口で、入れそうな保育園の一覧をもらった。家から一番近い園には、二十人待ちと書いてあった。</t>
+役所の窓口で、入れそうな保育園の一覧をもらった。家から一番近い園には、二十人待ちと書いてあった。
+〔次〕
+二人目の保育園探しがはじまった。
+上の子と同じ園に入れるかどうか、窓口の人は「ご兄弟は点数が加わります」とだけ言った。</t>
         </is>
       </c>
       <c r="J190" s="6" t="inlineStr">
@@ -24166,7 +26354,10 @@
       <c r="I192" s="6" t="inlineStr">
         <is>
           <t>子どもの友達の多くが、何か習い事をしていた。
-帰り道、子どもが「〇〇ちゃん、ピアノやってるんだって」と三回言った。</t>
+帰り道、子どもが「〇〇ちゃん、ピアノやってるんだって」と三回言った。
+〔次〕
+下の子も、習い事をしたいと言いだした。
+上の子が「やめといたほうがいいよ」と、先輩の顔で言った。</t>
         </is>
       </c>
       <c r="J192" s="6" t="inlineStr">
@@ -24388,7 +26579,10 @@
       <c r="I195" s="6" t="inlineStr">
         <is>
           <t>朝、子どもの部屋のドアの前で「今日も行けない」と小さな声がした。
-ランドセルが、制服のかばんに変わったばかりだった。</t>
+ランドセルが、制服のかばんに変わったばかりだった。
+〔次〕
+下の子も、朝、玄関で動けなくなった。
+上の子が、黙って弟か妹の靴をそろえていた。</t>
         </is>
       </c>
       <c r="J195" s="6" t="inlineStr">
@@ -25400,7 +27594,10 @@
       <c r="I210" s="6" t="inlineStr">
         <is>
           <t>子どもを園に送ったあとの帰り道、パートの募集の貼り紙が目に入った。
-「週三日から」の文字を、しばらく眺めていた。</t>
+「週三日から」の文字を、しばらく眺めていた。
+〔次〕
+求人サイトを、寝る前に眺めるのが癖になった。
+「ブランク歓迎」の文字に、いちいち指が止まった。</t>
         </is>
       </c>
       <c r="J210" s="6" t="inlineStr">
